--- a/docs/reports/SNDK.xlsx
+++ b/docs/reports/SNDK.xlsx
@@ -8,8 +8,8 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cover" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Financial Model" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SWS Valuation" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Target Price" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Financial Model" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assumptions" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WACC" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Model" sheetId="6" state="visible" r:id="rId6"/>
@@ -144,7 +144,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -160,20 +160,16 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="11" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="169" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="1" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="169" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="5" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="5" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -183,6 +179,7 @@
     <xf numFmtId="165" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="7" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="9" fillId="4" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="169" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -570,7 +567,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Technology · Standard (2-Stage FCFE) · generated 2026-07-09 · data: yfinance</t>
+          <t>Technology · Standard (forward multiples + DCF) · generated 2026-10-13 · data: Yahoo snapshot as of 2026-07-09</t>
         </is>
       </c>
     </row>
@@ -588,7 +585,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>DCF value per share</t>
+          <t>DCF value per share (one lens)</t>
         </is>
       </c>
       <c r="B5" s="4">
@@ -610,11 +607,11 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Blended fair value (report)</t>
+          <t>12-month price target (report)</t>
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>389747.6262116135</v>
+        <v>1343.662376005138</v>
       </c>
     </row>
     <row r="8">
@@ -699,7 +696,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>As reported by yfinance (USDmm). Hardcoded actuals.</t>
+          <t>As reported by Yahoo snapshot as of 2026-07-09 (USDmm). Hardcoded actuals.</t>
         </is>
       </c>
     </row>
@@ -726,7 +723,7 @@
           <t>Ordinary Shares Number</t>
         </is>
       </c>
-      <c r="C5" s="29" t="n">
+      <c r="C5" s="25" t="n">
         <v>146</v>
       </c>
     </row>
@@ -736,7 +733,7 @@
           <t>Share Issued</t>
         </is>
       </c>
-      <c r="C6" s="29" t="n">
+      <c r="C6" s="25" t="n">
         <v>146</v>
       </c>
     </row>
@@ -746,10 +743,10 @@
           <t>Net Debt</t>
         </is>
       </c>
-      <c r="B7" s="29" t="n">
+      <c r="B7" s="25" t="n">
         <v>486</v>
       </c>
-      <c r="C7" s="29" t="n">
+      <c r="C7" s="25" t="n">
         <v>368</v>
       </c>
     </row>
@@ -759,10 +756,10 @@
           <t>Total Debt</t>
         </is>
       </c>
-      <c r="B8" s="29" t="n">
+      <c r="B8" s="25" t="n">
         <v>985</v>
       </c>
-      <c r="C8" s="29" t="n">
+      <c r="C8" s="25" t="n">
         <v>2042</v>
       </c>
     </row>
@@ -772,10 +769,10 @@
           <t>Tangible Book Value</t>
         </is>
       </c>
-      <c r="B9" s="29" t="n">
+      <c r="B9" s="25" t="n">
         <v>3875</v>
       </c>
-      <c r="C9" s="29" t="n">
+      <c r="C9" s="25" t="n">
         <v>4217</v>
       </c>
     </row>
@@ -785,10 +782,10 @@
           <t>Invested Capital</t>
         </is>
       </c>
-      <c r="B10" s="29" t="n">
+      <c r="B10" s="25" t="n">
         <v>11896</v>
       </c>
-      <c r="C10" s="29" t="n">
+      <c r="C10" s="25" t="n">
         <v>11065</v>
       </c>
     </row>
@@ -798,10 +795,10 @@
           <t>Working Capital</t>
         </is>
       </c>
-      <c r="B11" s="29" t="n">
+      <c r="B11" s="25" t="n">
         <v>1425</v>
       </c>
-      <c r="C11" s="29" t="n">
+      <c r="C11" s="25" t="n">
         <v>3659</v>
       </c>
     </row>
@@ -811,10 +808,10 @@
           <t>Net Tangible Assets</t>
         </is>
       </c>
-      <c r="B12" s="29" t="n">
+      <c r="B12" s="25" t="n">
         <v>3875</v>
       </c>
-      <c r="C12" s="29" t="n">
+      <c r="C12" s="25" t="n">
         <v>4217</v>
       </c>
     </row>
@@ -824,10 +821,10 @@
           <t>Capital Lease Obligations</t>
         </is>
       </c>
-      <c r="B13" s="29" t="n">
+      <c r="B13" s="25" t="n">
         <v>171</v>
       </c>
-      <c r="C13" s="29" t="n">
+      <c r="C13" s="25" t="n">
         <v>193</v>
       </c>
     </row>
@@ -837,10 +834,10 @@
           <t>Common Stock Equity</t>
         </is>
       </c>
-      <c r="B14" s="29" t="n">
+      <c r="B14" s="25" t="n">
         <v>11082</v>
       </c>
-      <c r="C14" s="29" t="n">
+      <c r="C14" s="25" t="n">
         <v>9216</v>
       </c>
     </row>
@@ -850,10 +847,10 @@
           <t>Total Capitalization</t>
         </is>
       </c>
-      <c r="B15" s="29" t="n">
+      <c r="B15" s="25" t="n">
         <v>11082</v>
       </c>
-      <c r="C15" s="29" t="n">
+      <c r="C15" s="25" t="n">
         <v>11045</v>
       </c>
     </row>
@@ -863,10 +860,10 @@
           <t>Total Equity Gross Minority Interest</t>
         </is>
       </c>
-      <c r="B16" s="29" t="n">
+      <c r="B16" s="25" t="n">
         <v>11082</v>
       </c>
-      <c r="C16" s="29" t="n">
+      <c r="C16" s="25" t="n">
         <v>9216</v>
       </c>
     </row>
@@ -876,10 +873,10 @@
           <t>Stockholders Equity</t>
         </is>
       </c>
-      <c r="B17" s="29" t="n">
+      <c r="B17" s="25" t="n">
         <v>11082</v>
       </c>
-      <c r="C17" s="29" t="n">
+      <c r="C17" s="25" t="n">
         <v>9216</v>
       </c>
     </row>
@@ -889,10 +886,10 @@
           <t>Gains Losses Not Affecting Retained Earnings</t>
         </is>
       </c>
-      <c r="B18" s="29" t="n">
+      <c r="B18" s="25" t="n">
         <v>-452</v>
       </c>
-      <c r="C18" s="29" t="n">
+      <c r="C18" s="25" t="n">
         <v>-249</v>
       </c>
     </row>
@@ -902,10 +899,10 @@
           <t>Other Equity Adjustments</t>
         </is>
       </c>
-      <c r="B19" s="29" t="n">
+      <c r="B19" s="25" t="n">
         <v>-452</v>
       </c>
-      <c r="C19" s="29" t="n">
+      <c r="C19" s="25" t="n">
         <v>-249</v>
       </c>
     </row>
@@ -915,10 +912,10 @@
           <t>Retained Earnings</t>
         </is>
       </c>
-      <c r="B20" s="29" t="n">
+      <c r="B20" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="C20" s="29" t="n">
+      <c r="C20" s="25" t="n">
         <v>-1784</v>
       </c>
     </row>
@@ -928,10 +925,10 @@
           <t>Additional Paid In Capital</t>
         </is>
       </c>
-      <c r="B21" s="29" t="n">
+      <c r="B21" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="C21" s="29" t="n">
+      <c r="C21" s="25" t="n">
         <v>11248</v>
       </c>
     </row>
@@ -941,10 +938,10 @@
           <t>Capital Stock</t>
         </is>
       </c>
-      <c r="B22" s="29" t="n">
+      <c r="B22" s="25" t="n">
         <v>11534</v>
       </c>
-      <c r="C22" s="29" t="n">
+      <c r="C22" s="25" t="n">
         <v>1</v>
       </c>
     </row>
@@ -954,10 +951,10 @@
           <t>Common Stock</t>
         </is>
       </c>
-      <c r="B23" s="29" t="n">
+      <c r="B23" s="25" t="n">
         <v>11534</v>
       </c>
-      <c r="C23" s="29" t="n">
+      <c r="C23" s="25" t="n">
         <v>1</v>
       </c>
     </row>
@@ -967,10 +964,10 @@
           <t>Total Liabilities Net Minority Interest</t>
         </is>
       </c>
-      <c r="B24" s="29" t="n">
+      <c r="B24" s="25" t="n">
         <v>2424</v>
       </c>
-      <c r="C24" s="29" t="n">
+      <c r="C24" s="25" t="n">
         <v>3769</v>
       </c>
     </row>
@@ -980,10 +977,10 @@
           <t>Total Non Current Liabilities Net Minority Interest</t>
         </is>
       </c>
-      <c r="B25" s="29" t="n">
+      <c r="B25" s="25" t="n">
         <v>301</v>
       </c>
-      <c r="C25" s="29" t="n">
+      <c r="C25" s="25" t="n">
         <v>2342</v>
       </c>
     </row>
@@ -993,10 +990,10 @@
           <t>Other Non Current Liabilities</t>
         </is>
       </c>
-      <c r="B26" s="29" t="n">
+      <c r="B26" s="25" t="n">
         <v>59</v>
       </c>
-      <c r="C26" s="29" t="n">
+      <c r="C26" s="25" t="n">
         <v>62</v>
       </c>
     </row>
@@ -1006,10 +1003,10 @@
           <t>Tradeand Other Payables Non Current</t>
         </is>
       </c>
-      <c r="B27" s="29" t="n">
+      <c r="B27" s="25" t="n">
         <v>56</v>
       </c>
-      <c r="C27" s="29" t="n">
+      <c r="C27" s="25" t="n">
         <v>241</v>
       </c>
     </row>
@@ -1019,10 +1016,10 @@
           <t>Non Current Deferred Liabilities</t>
         </is>
       </c>
-      <c r="B28" s="29" t="n">
+      <c r="B28" s="25" t="n">
         <v>15</v>
       </c>
-      <c r="C28" s="29" t="n">
+      <c r="C28" s="25" t="n">
         <v>17</v>
       </c>
     </row>
@@ -1032,10 +1029,10 @@
           <t>Non Current Deferred Taxes Liabilities</t>
         </is>
       </c>
-      <c r="B29" s="29" t="n">
+      <c r="B29" s="25" t="n">
         <v>15</v>
       </c>
-      <c r="C29" s="29" t="n">
+      <c r="C29" s="25" t="n">
         <v>17</v>
       </c>
     </row>
@@ -1045,10 +1042,10 @@
           <t>Long Term Debt And Capital Lease Obligation</t>
         </is>
       </c>
-      <c r="B30" s="29" t="n">
+      <c r="B30" s="25" t="n">
         <v>171</v>
       </c>
-      <c r="C30" s="29" t="n">
+      <c r="C30" s="25" t="n">
         <v>2022</v>
       </c>
     </row>
@@ -1058,10 +1055,10 @@
           <t>Long Term Capital Lease Obligation</t>
         </is>
       </c>
-      <c r="B31" s="29" t="n">
+      <c r="B31" s="25" t="n">
         <v>171</v>
       </c>
-      <c r="C31" s="29" t="n">
+      <c r="C31" s="25" t="n">
         <v>193</v>
       </c>
     </row>
@@ -1071,7 +1068,7 @@
           <t>Long Term Debt</t>
         </is>
       </c>
-      <c r="C32" s="29" t="n">
+      <c r="C32" s="25" t="n">
         <v>1829</v>
       </c>
     </row>
@@ -1081,10 +1078,10 @@
           <t>Current Liabilities</t>
         </is>
       </c>
-      <c r="B33" s="29" t="n">
+      <c r="B33" s="25" t="n">
         <v>2123</v>
       </c>
-      <c r="C33" s="29" t="n">
+      <c r="C33" s="25" t="n">
         <v>1427</v>
       </c>
     </row>
@@ -1094,10 +1091,10 @@
           <t>Current Debt And Capital Lease Obligation</t>
         </is>
       </c>
-      <c r="B34" s="29" t="n">
+      <c r="B34" s="25" t="n">
         <v>814</v>
       </c>
-      <c r="C34" s="29" t="n">
+      <c r="C34" s="25" t="n">
         <v>20</v>
       </c>
     </row>
@@ -1107,10 +1104,10 @@
           <t>Current Debt</t>
         </is>
       </c>
-      <c r="B35" s="29" t="n">
+      <c r="B35" s="25" t="n">
         <v>814</v>
       </c>
-      <c r="C35" s="29" t="n">
+      <c r="C35" s="25" t="n">
         <v>20</v>
       </c>
     </row>
@@ -1120,7 +1117,7 @@
           <t>Other Current Borrowings</t>
         </is>
       </c>
-      <c r="C36" s="29" t="n">
+      <c r="C36" s="25" t="n">
         <v>20</v>
       </c>
     </row>
@@ -1130,10 +1127,10 @@
           <t>Current Notes Payable</t>
         </is>
       </c>
-      <c r="B37" s="29" t="n">
+      <c r="B37" s="25" t="n">
         <v>814</v>
       </c>
-      <c r="C37" s="29" t="n">
+      <c r="C37" s="25" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1143,10 +1140,10 @@
           <t>Payables And Accrued Expenses</t>
         </is>
       </c>
-      <c r="B38" s="29" t="n">
+      <c r="B38" s="25" t="n">
         <v>1309</v>
       </c>
-      <c r="C38" s="29" t="n">
+      <c r="C38" s="25" t="n">
         <v>1407</v>
       </c>
     </row>
@@ -1156,10 +1153,10 @@
           <t>Current Accrued Expenses</t>
         </is>
       </c>
-      <c r="B39" s="29" t="n">
+      <c r="B39" s="25" t="n">
         <v>619</v>
       </c>
-      <c r="C39" s="29" t="n">
+      <c r="C39" s="25" t="n">
         <v>598</v>
       </c>
     </row>
@@ -1169,10 +1166,10 @@
           <t>Payables</t>
         </is>
       </c>
-      <c r="B40" s="29" t="n">
+      <c r="B40" s="25" t="n">
         <v>690</v>
       </c>
-      <c r="C40" s="29" t="n">
+      <c r="C40" s="25" t="n">
         <v>809</v>
       </c>
     </row>
@@ -1182,10 +1179,10 @@
           <t>Dueto Related Parties Current</t>
         </is>
       </c>
-      <c r="B41" s="29" t="n">
+      <c r="B41" s="25" t="n">
         <v>313</v>
       </c>
-      <c r="C41" s="29" t="n">
+      <c r="C41" s="25" t="n">
         <v>400</v>
       </c>
     </row>
@@ -1195,10 +1192,10 @@
           <t>Total Tax Payable</t>
         </is>
       </c>
-      <c r="B42" s="29" t="n">
+      <c r="B42" s="25" t="n">
         <v>20</v>
       </c>
-      <c r="C42" s="29" t="n">
+      <c r="C42" s="25" t="n">
         <v>43</v>
       </c>
     </row>
@@ -1208,10 +1205,10 @@
           <t>Income Tax Payable</t>
         </is>
       </c>
-      <c r="B43" s="29" t="n">
+      <c r="B43" s="25" t="n">
         <v>20</v>
       </c>
-      <c r="C43" s="29" t="n">
+      <c r="C43" s="25" t="n">
         <v>43</v>
       </c>
     </row>
@@ -1221,10 +1218,10 @@
           <t>Accounts Payable</t>
         </is>
       </c>
-      <c r="B44" s="29" t="n">
+      <c r="B44" s="25" t="n">
         <v>357</v>
       </c>
-      <c r="C44" s="29" t="n">
+      <c r="C44" s="25" t="n">
         <v>366</v>
       </c>
     </row>
@@ -1234,10 +1231,10 @@
           <t>Total Assets</t>
         </is>
       </c>
-      <c r="B45" s="29" t="n">
+      <c r="B45" s="25" t="n">
         <v>13506</v>
       </c>
-      <c r="C45" s="29" t="n">
+      <c r="C45" s="25" t="n">
         <v>12985</v>
       </c>
     </row>
@@ -1247,10 +1244,10 @@
           <t>Total Non Current Assets</t>
         </is>
       </c>
-      <c r="B46" s="29" t="n">
+      <c r="B46" s="25" t="n">
         <v>9958</v>
       </c>
-      <c r="C46" s="29" t="n">
+      <c r="C46" s="25" t="n">
         <v>7899</v>
       </c>
     </row>
@@ -1260,10 +1257,10 @@
           <t>Other Non Current Assets</t>
         </is>
       </c>
-      <c r="B47" s="29" t="n">
+      <c r="B47" s="25" t="n">
         <v>852</v>
       </c>
-      <c r="C47" s="29" t="n">
+      <c r="C47" s="25" t="n">
         <v>1489</v>
       </c>
     </row>
@@ -1273,10 +1270,10 @@
           <t>Non Current Deferred Assets</t>
         </is>
       </c>
-      <c r="B48" s="29" t="n">
+      <c r="B48" s="25" t="n">
         <v>96</v>
       </c>
-      <c r="C48" s="29" t="n">
+      <c r="C48" s="25" t="n">
         <v>58</v>
       </c>
     </row>
@@ -1286,10 +1283,10 @@
           <t>Non Current Deferred Taxes Assets</t>
         </is>
       </c>
-      <c r="B49" s="29" t="n">
+      <c r="B49" s="25" t="n">
         <v>96</v>
       </c>
-      <c r="C49" s="29" t="n">
+      <c r="C49" s="25" t="n">
         <v>58</v>
       </c>
     </row>
@@ -1299,10 +1296,10 @@
           <t>Non Current Note Receivables</t>
         </is>
       </c>
-      <c r="B50" s="29" t="n">
+      <c r="B50" s="25" t="n">
         <v>1001</v>
       </c>
-      <c r="C50" s="29" t="n">
+      <c r="C50" s="25" t="n">
         <v>654</v>
       </c>
     </row>
@@ -1312,10 +1309,10 @@
           <t>Non Current Accounts Receivable</t>
         </is>
       </c>
-      <c r="B51" s="29" t="n">
+      <c r="B51" s="25" t="n">
         <v>11</v>
       </c>
-      <c r="C51" s="29" t="n">
+      <c r="C51" s="25" t="n">
         <v>80</v>
       </c>
     </row>
@@ -1325,10 +1322,10 @@
           <t>Goodwill And Other Intangible Assets</t>
         </is>
       </c>
-      <c r="B52" s="29" t="n">
+      <c r="B52" s="25" t="n">
         <v>7207</v>
       </c>
-      <c r="C52" s="29" t="n">
+      <c r="C52" s="25" t="n">
         <v>4999</v>
       </c>
     </row>
@@ -1338,10 +1335,10 @@
           <t>Goodwill</t>
         </is>
       </c>
-      <c r="B53" s="29" t="n">
+      <c r="B53" s="25" t="n">
         <v>7207</v>
       </c>
-      <c r="C53" s="29" t="n">
+      <c r="C53" s="25" t="n">
         <v>4999</v>
       </c>
     </row>
@@ -1351,10 +1348,10 @@
           <t>Net PPE</t>
         </is>
       </c>
-      <c r="B54" s="29" t="n">
+      <c r="B54" s="25" t="n">
         <v>791</v>
       </c>
-      <c r="C54" s="29" t="n">
+      <c r="C54" s="25" t="n">
         <v>619</v>
       </c>
     </row>
@@ -1364,10 +1361,10 @@
           <t>Accumulated Depreciation</t>
         </is>
       </c>
-      <c r="B55" s="29" t="n">
+      <c r="B55" s="25" t="n">
         <v>-2203</v>
       </c>
-      <c r="C55" s="29" t="n">
+      <c r="C55" s="25" t="n">
         <v>-1506</v>
       </c>
     </row>
@@ -1377,10 +1374,10 @@
           <t>Gross PPE</t>
         </is>
       </c>
-      <c r="B56" s="29" t="n">
+      <c r="B56" s="25" t="n">
         <v>2994</v>
       </c>
-      <c r="C56" s="29" t="n">
+      <c r="C56" s="25" t="n">
         <v>2125</v>
       </c>
     </row>
@@ -1390,10 +1387,10 @@
           <t>Construction In Progress</t>
         </is>
       </c>
-      <c r="B57" s="29" t="n">
+      <c r="B57" s="25" t="n">
         <v>108</v>
       </c>
-      <c r="C57" s="29" t="n">
+      <c r="C57" s="25" t="n">
         <v>51</v>
       </c>
     </row>
@@ -1403,10 +1400,10 @@
           <t>Machinery Furniture Equipment</t>
         </is>
       </c>
-      <c r="B58" s="29" t="n">
+      <c r="B58" s="25" t="n">
         <v>2479</v>
       </c>
-      <c r="C58" s="29" t="n">
+      <c r="C58" s="25" t="n">
         <v>1674</v>
       </c>
     </row>
@@ -1416,10 +1413,10 @@
           <t>Buildings And Improvements</t>
         </is>
       </c>
-      <c r="B59" s="29" t="n">
+      <c r="B59" s="25" t="n">
         <v>397</v>
       </c>
-      <c r="C59" s="29" t="n">
+      <c r="C59" s="25" t="n">
         <v>390</v>
       </c>
     </row>
@@ -1429,10 +1426,10 @@
           <t>Land And Improvements</t>
         </is>
       </c>
-      <c r="B60" s="29" t="n">
+      <c r="B60" s="25" t="n">
         <v>10</v>
       </c>
-      <c r="C60" s="29" t="n">
+      <c r="C60" s="25" t="n">
         <v>10</v>
       </c>
     </row>
@@ -1442,10 +1439,10 @@
           <t>Properties</t>
         </is>
       </c>
-      <c r="B61" s="29" t="n">
+      <c r="B61" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="C61" s="29" t="n">
+      <c r="C61" s="25" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1455,10 +1452,10 @@
           <t>Current Assets</t>
         </is>
       </c>
-      <c r="B62" s="29" t="n">
+      <c r="B62" s="25" t="n">
         <v>3548</v>
       </c>
-      <c r="C62" s="29" t="n">
+      <c r="C62" s="25" t="n">
         <v>5086</v>
       </c>
     </row>
@@ -1468,10 +1465,10 @@
           <t>Other Current Assets</t>
         </is>
       </c>
-      <c r="B63" s="29" t="n">
+      <c r="B63" s="25" t="n">
         <v>221</v>
       </c>
-      <c r="C63" s="29" t="n">
+      <c r="C63" s="25" t="n">
         <v>392</v>
       </c>
     </row>
@@ -1481,10 +1478,10 @@
           <t>Inventory</t>
         </is>
       </c>
-      <c r="B64" s="29" t="n">
+      <c r="B64" s="25" t="n">
         <v>1955</v>
       </c>
-      <c r="C64" s="29" t="n">
+      <c r="C64" s="25" t="n">
         <v>2079</v>
       </c>
     </row>
@@ -1494,10 +1491,10 @@
           <t>Finished Goods</t>
         </is>
       </c>
-      <c r="B65" s="29" t="n">
+      <c r="B65" s="25" t="n">
         <v>320</v>
       </c>
-      <c r="C65" s="29" t="n">
+      <c r="C65" s="25" t="n">
         <v>300</v>
       </c>
     </row>
@@ -1507,10 +1504,10 @@
           <t>Work In Process</t>
         </is>
       </c>
-      <c r="B66" s="29" t="n">
+      <c r="B66" s="25" t="n">
         <v>237</v>
       </c>
-      <c r="C66" s="29" t="n">
+      <c r="C66" s="25" t="n">
         <v>262</v>
       </c>
     </row>
@@ -1520,10 +1517,10 @@
           <t>Raw Materials</t>
         </is>
       </c>
-      <c r="B67" s="29" t="n">
+      <c r="B67" s="25" t="n">
         <v>1398</v>
       </c>
-      <c r="C67" s="29" t="n">
+      <c r="C67" s="25" t="n">
         <v>1517</v>
       </c>
     </row>
@@ -1533,10 +1530,10 @@
           <t>Receivables</t>
         </is>
       </c>
-      <c r="B68" s="29" t="n">
+      <c r="B68" s="25" t="n">
         <v>1044</v>
       </c>
-      <c r="C68" s="29" t="n">
+      <c r="C68" s="25" t="n">
         <v>1134</v>
       </c>
     </row>
@@ -1546,10 +1543,10 @@
           <t>Taxes Receivable</t>
         </is>
       </c>
-      <c r="B69" s="29" t="n">
+      <c r="B69" s="25" t="n">
         <v>7</v>
       </c>
-      <c r="C69" s="29" t="n">
+      <c r="C69" s="25" t="n">
         <v>66</v>
       </c>
     </row>
@@ -1559,10 +1556,10 @@
           <t>Notes Receivable</t>
         </is>
       </c>
-      <c r="B70" s="29" t="n">
+      <c r="B70" s="25" t="n">
         <v>102</v>
       </c>
-      <c r="C70" s="29" t="n">
+      <c r="C70" s="25" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1572,10 +1569,10 @@
           <t>Accounts Receivable</t>
         </is>
       </c>
-      <c r="B71" s="29" t="n">
+      <c r="B71" s="25" t="n">
         <v>935</v>
       </c>
-      <c r="C71" s="29" t="n">
+      <c r="C71" s="25" t="n">
         <v>1068</v>
       </c>
     </row>
@@ -1585,10 +1582,10 @@
           <t>Cash Cash Equivalents And Short Term Investments</t>
         </is>
       </c>
-      <c r="B72" s="29" t="n">
+      <c r="B72" s="25" t="n">
         <v>328</v>
       </c>
-      <c r="C72" s="29" t="n">
+      <c r="C72" s="25" t="n">
         <v>1481</v>
       </c>
     </row>
@@ -1598,10 +1595,10 @@
           <t>Cash And Cash Equivalents</t>
         </is>
       </c>
-      <c r="B73" s="29" t="n">
+      <c r="B73" s="25" t="n">
         <v>328</v>
       </c>
-      <c r="C73" s="29" t="n">
+      <c r="C73" s="25" t="n">
         <v>1481</v>
       </c>
     </row>
@@ -1635,7 +1632,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>As reported by yfinance (USDmm). Hardcoded actuals.</t>
+          <t>As reported by Yahoo snapshot as of 2026-07-09 (USDmm). Hardcoded actuals.</t>
         </is>
       </c>
     </row>
@@ -1667,13 +1664,13 @@
           <t>Free Cash Flow</t>
         </is>
       </c>
-      <c r="B5" s="29" t="n">
+      <c r="B5" s="25" t="n">
         <v>-932</v>
       </c>
-      <c r="C5" s="29" t="n">
+      <c r="C5" s="25" t="n">
         <v>-475</v>
       </c>
-      <c r="D5" s="29" t="n">
+      <c r="D5" s="25" t="n">
         <v>-120</v>
       </c>
     </row>
@@ -1683,13 +1680,13 @@
           <t>Repayment Of Debt</t>
         </is>
       </c>
-      <c r="B6" s="29" t="n">
+      <c r="B6" s="25" t="n">
         <v>-86</v>
       </c>
-      <c r="C6" s="29" t="n">
+      <c r="C6" s="25" t="n">
         <v>-272</v>
       </c>
-      <c r="D6" s="29" t="n">
+      <c r="D6" s="25" t="n">
         <v>-176</v>
       </c>
     </row>
@@ -1699,13 +1696,13 @@
           <t>Issuance Of Debt</t>
         </is>
       </c>
-      <c r="B7" s="29" t="n">
+      <c r="B7" s="25" t="n">
         <v>270</v>
       </c>
-      <c r="C7" s="29" t="n">
+      <c r="C7" s="25" t="n">
         <v>14</v>
       </c>
-      <c r="D7" s="29" t="n">
+      <c r="D7" s="25" t="n">
         <v>2621</v>
       </c>
     </row>
@@ -1715,13 +1712,13 @@
           <t>Capital Expenditure</t>
         </is>
       </c>
-      <c r="B8" s="29" t="n">
+      <c r="B8" s="25" t="n">
         <v>-219</v>
       </c>
-      <c r="C8" s="29" t="n">
+      <c r="C8" s="25" t="n">
         <v>-166</v>
       </c>
-      <c r="D8" s="29" t="n">
+      <c r="D8" s="25" t="n">
         <v>-204</v>
       </c>
     </row>
@@ -1731,13 +1728,13 @@
           <t>Interest Paid Supplemental Data</t>
         </is>
       </c>
-      <c r="B9" s="29" t="n">
+      <c r="B9" s="25" t="n">
         <v>7</v>
       </c>
-      <c r="C9" s="29" t="n">
+      <c r="C9" s="25" t="n">
         <v>12</v>
       </c>
-      <c r="D9" s="29" t="n">
+      <c r="D9" s="25" t="n">
         <v>139</v>
       </c>
     </row>
@@ -1747,13 +1744,13 @@
           <t>Income Tax Paid Supplemental Data</t>
         </is>
       </c>
-      <c r="B10" s="29" t="n">
+      <c r="B10" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="C10" s="29" t="n">
+      <c r="C10" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="D10" s="29" t="n">
+      <c r="D10" s="25" t="n">
         <v>50</v>
       </c>
     </row>
@@ -1763,13 +1760,13 @@
           <t>End Cash Position</t>
         </is>
       </c>
-      <c r="B11" s="29" t="n">
+      <c r="B11" s="25" t="n">
         <v>292</v>
       </c>
-      <c r="C11" s="29" t="n">
+      <c r="C11" s="25" t="n">
         <v>328</v>
       </c>
-      <c r="D11" s="29" t="n">
+      <c r="D11" s="25" t="n">
         <v>1481</v>
       </c>
     </row>
@@ -1779,13 +1776,13 @@
           <t>Beginning Cash Position</t>
         </is>
       </c>
-      <c r="B12" s="29" t="n">
+      <c r="B12" s="25" t="n">
         <v>335</v>
       </c>
-      <c r="C12" s="29" t="n">
+      <c r="C12" s="25" t="n">
         <v>292</v>
       </c>
-      <c r="D12" s="29" t="n">
+      <c r="D12" s="25" t="n">
         <v>328</v>
       </c>
     </row>
@@ -1795,13 +1792,13 @@
           <t>Effect Of Exchange Rate Changes</t>
         </is>
       </c>
-      <c r="B13" s="29" t="n">
+      <c r="B13" s="25" t="n">
         <v>-1</v>
       </c>
-      <c r="C13" s="29" t="n">
+      <c r="C13" s="25" t="n">
         <v>-1</v>
       </c>
-      <c r="D13" s="29" t="n">
+      <c r="D13" s="25" t="n">
         <v>-5</v>
       </c>
     </row>
@@ -1811,13 +1808,13 @@
           <t>Changes In Cash</t>
         </is>
       </c>
-      <c r="B14" s="29" t="n">
+      <c r="B14" s="25" t="n">
         <v>-42</v>
       </c>
-      <c r="C14" s="29" t="n">
+      <c r="C14" s="25" t="n">
         <v>37</v>
       </c>
-      <c r="D14" s="29" t="n">
+      <c r="D14" s="25" t="n">
         <v>1158</v>
       </c>
     </row>
@@ -1827,13 +1824,13 @@
           <t>Financing Cash Flow</t>
         </is>
       </c>
-      <c r="B15" s="29" t="n">
+      <c r="B15" s="25" t="n">
         <v>860</v>
       </c>
-      <c r="C15" s="29" t="n">
+      <c r="C15" s="25" t="n">
         <v>136</v>
       </c>
-      <c r="D15" s="29" t="n">
+      <c r="D15" s="25" t="n">
         <v>518</v>
       </c>
     </row>
@@ -1843,13 +1840,13 @@
           <t>Cash Flow From Continuing Financing Activities</t>
         </is>
       </c>
-      <c r="B16" s="29" t="n">
+      <c r="B16" s="25" t="n">
         <v>860</v>
       </c>
-      <c r="C16" s="29" t="n">
+      <c r="C16" s="25" t="n">
         <v>136</v>
       </c>
-      <c r="D16" s="29" t="n">
+      <c r="D16" s="25" t="n">
         <v>518</v>
       </c>
     </row>
@@ -1859,13 +1856,13 @@
           <t>Net Other Financing Charges</t>
         </is>
       </c>
-      <c r="B17" s="29" t="n">
+      <c r="B17" s="25" t="n">
         <v>676</v>
       </c>
-      <c r="C17" s="29" t="n">
+      <c r="C17" s="25" t="n">
         <v>394</v>
       </c>
-      <c r="D17" s="29" t="n">
+      <c r="D17" s="25" t="n">
         <v>-1932</v>
       </c>
     </row>
@@ -1875,13 +1872,13 @@
           <t>Proceeds From Stock Option Exercised</t>
         </is>
       </c>
-      <c r="B18" s="29" t="n">
+      <c r="B18" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="C18" s="29" t="n">
+      <c r="C18" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="D18" s="29" t="n">
+      <c r="D18" s="25" t="n">
         <v>5</v>
       </c>
     </row>
@@ -1891,13 +1888,13 @@
           <t>Net Issuance Payments Of Debt</t>
         </is>
       </c>
-      <c r="B19" s="29" t="n">
+      <c r="B19" s="25" t="n">
         <v>184</v>
       </c>
-      <c r="C19" s="29" t="n">
+      <c r="C19" s="25" t="n">
         <v>-258</v>
       </c>
-      <c r="D19" s="29" t="n">
+      <c r="D19" s="25" t="n">
         <v>2445</v>
       </c>
     </row>
@@ -1907,13 +1904,13 @@
           <t>Net Short Term Debt Issuance</t>
         </is>
       </c>
-      <c r="B20" s="29" t="n">
+      <c r="B20" s="25" t="n">
         <v>184</v>
       </c>
-      <c r="C20" s="29" t="n">
+      <c r="C20" s="25" t="n">
         <v>-258</v>
       </c>
-      <c r="D20" s="29" t="n">
+      <c r="D20" s="25" t="n">
         <v>575</v>
       </c>
     </row>
@@ -1923,13 +1920,13 @@
           <t>Short Term Debt Payments</t>
         </is>
       </c>
-      <c r="B21" s="29" t="n">
+      <c r="B21" s="25" t="n">
         <v>-86</v>
       </c>
-      <c r="C21" s="29" t="n">
+      <c r="C21" s="25" t="n">
         <v>-272</v>
       </c>
-      <c r="D21" s="29" t="n">
+      <c r="D21" s="25" t="n">
         <v>-76</v>
       </c>
     </row>
@@ -1939,13 +1936,13 @@
           <t>Short Term Debt Issuance</t>
         </is>
       </c>
-      <c r="B22" s="29" t="n">
+      <c r="B22" s="25" t="n">
         <v>270</v>
       </c>
-      <c r="C22" s="29" t="n">
+      <c r="C22" s="25" t="n">
         <v>14</v>
       </c>
-      <c r="D22" s="29" t="n">
+      <c r="D22" s="25" t="n">
         <v>651</v>
       </c>
     </row>
@@ -1955,13 +1952,13 @@
           <t>Net Long Term Debt Issuance</t>
         </is>
       </c>
-      <c r="B23" s="29" t="n">
+      <c r="B23" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="C23" s="29" t="n">
+      <c r="C23" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="D23" s="29" t="n">
+      <c r="D23" s="25" t="n">
         <v>1870</v>
       </c>
     </row>
@@ -1971,13 +1968,13 @@
           <t>Long Term Debt Payments</t>
         </is>
       </c>
-      <c r="B24" s="29" t="n">
+      <c r="B24" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="C24" s="29" t="n">
+      <c r="C24" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="D24" s="29" t="n">
+      <c r="D24" s="25" t="n">
         <v>-100</v>
       </c>
     </row>
@@ -1987,13 +1984,13 @@
           <t>Long Term Debt Issuance</t>
         </is>
       </c>
-      <c r="B25" s="29" t="n">
+      <c r="B25" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="C25" s="29" t="n">
+      <c r="C25" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="D25" s="29" t="n">
+      <c r="D25" s="25" t="n">
         <v>1970</v>
       </c>
     </row>
@@ -2003,13 +2000,13 @@
           <t>Investing Cash Flow</t>
         </is>
       </c>
-      <c r="B26" s="29" t="n">
+      <c r="B26" s="25" t="n">
         <v>-189</v>
       </c>
-      <c r="C26" s="29" t="n">
+      <c r="C26" s="25" t="n">
         <v>210</v>
       </c>
-      <c r="D26" s="29" t="n">
+      <c r="D26" s="25" t="n">
         <v>556</v>
       </c>
     </row>
@@ -2019,13 +2016,13 @@
           <t>Cash Flow From Continuing Investing Activities</t>
         </is>
       </c>
-      <c r="B27" s="29" t="n">
+      <c r="B27" s="25" t="n">
         <v>-189</v>
       </c>
-      <c r="C27" s="29" t="n">
+      <c r="C27" s="25" t="n">
         <v>210</v>
       </c>
-      <c r="D27" s="29" t="n">
+      <c r="D27" s="25" t="n">
         <v>556</v>
       </c>
     </row>
@@ -2035,13 +2032,13 @@
           <t>Net Other Investing Changes</t>
         </is>
       </c>
-      <c r="B28" s="29" t="n">
+      <c r="B28" s="25" t="n">
         <v>14</v>
       </c>
-      <c r="C28" s="29" t="n">
+      <c r="C28" s="25" t="n">
         <v>239</v>
       </c>
-      <c r="D28" s="29" t="n">
+      <c r="D28" s="25" t="n">
         <v>182</v>
       </c>
     </row>
@@ -2051,13 +2048,13 @@
           <t>Dividends Received Cfi</t>
         </is>
       </c>
-      <c r="B29" s="29" t="n">
+      <c r="B29" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="C29" s="29" t="n">
+      <c r="C29" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="D29" s="29" t="n">
+      <c r="D29" s="25" t="n">
         <v>176</v>
       </c>
     </row>
@@ -2067,13 +2064,13 @@
           <t>Net Business Purchase And Sale</t>
         </is>
       </c>
-      <c r="B30" s="29" t="n">
+      <c r="B30" s="25" t="n">
         <v>16</v>
       </c>
-      <c r="C30" s="29" t="n">
+      <c r="C30" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="D30" s="29" t="n">
+      <c r="D30" s="25" t="n">
         <v>402</v>
       </c>
     </row>
@@ -2083,13 +2080,13 @@
           <t>Sale Of Business</t>
         </is>
       </c>
-      <c r="B31" s="29" t="n">
+      <c r="B31" s="25" t="n">
         <v>16</v>
       </c>
-      <c r="C31" s="29" t="n">
+      <c r="C31" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="D31" s="29" t="n">
+      <c r="D31" s="25" t="n">
         <v>402</v>
       </c>
     </row>
@@ -2099,13 +2096,13 @@
           <t>Net PPE Purchase And Sale</t>
         </is>
       </c>
-      <c r="B32" s="29" t="n">
+      <c r="B32" s="25" t="n">
         <v>-219</v>
       </c>
-      <c r="C32" s="29" t="n">
+      <c r="C32" s="25" t="n">
         <v>-29</v>
       </c>
-      <c r="D32" s="29" t="n">
+      <c r="D32" s="25" t="n">
         <v>-204</v>
       </c>
     </row>
@@ -2115,13 +2112,13 @@
           <t>Sale Of PPE</t>
         </is>
       </c>
-      <c r="B33" s="29" t="n">
+      <c r="B33" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="C33" s="29" t="n">
+      <c r="C33" s="25" t="n">
         <v>137</v>
       </c>
-      <c r="D33" s="29" t="n">
+      <c r="D33" s="25" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2131,13 +2128,13 @@
           <t>Purchase Of PPE</t>
         </is>
       </c>
-      <c r="B34" s="29" t="n">
+      <c r="B34" s="25" t="n">
         <v>-219</v>
       </c>
-      <c r="C34" s="29" t="n">
+      <c r="C34" s="25" t="n">
         <v>-166</v>
       </c>
-      <c r="D34" s="29" t="n">
+      <c r="D34" s="25" t="n">
         <v>-204</v>
       </c>
     </row>
@@ -2147,13 +2144,13 @@
           <t>Operating Cash Flow</t>
         </is>
       </c>
-      <c r="B35" s="29" t="n">
+      <c r="B35" s="25" t="n">
         <v>-713</v>
       </c>
-      <c r="C35" s="29" t="n">
+      <c r="C35" s="25" t="n">
         <v>-309</v>
       </c>
-      <c r="D35" s="29" t="n">
+      <c r="D35" s="25" t="n">
         <v>84</v>
       </c>
     </row>
@@ -2163,13 +2160,13 @@
           <t>Cash Flow From Continuing Operating Activities</t>
         </is>
       </c>
-      <c r="B36" s="29" t="n">
+      <c r="B36" s="25" t="n">
         <v>-713</v>
       </c>
-      <c r="C36" s="29" t="n">
+      <c r="C36" s="25" t="n">
         <v>-309</v>
       </c>
-      <c r="D36" s="29" t="n">
+      <c r="D36" s="25" t="n">
         <v>84</v>
       </c>
     </row>
@@ -2179,13 +2176,13 @@
           <t>Change In Working Capital</t>
         </is>
       </c>
-      <c r="B37" s="29" t="n">
+      <c r="B37" s="25" t="n">
         <v>197</v>
       </c>
-      <c r="C37" s="29" t="n">
+      <c r="C37" s="25" t="n">
         <v>-86</v>
       </c>
-      <c r="D37" s="29" t="n">
+      <c r="D37" s="25" t="n">
         <v>-380</v>
       </c>
     </row>
@@ -2195,13 +2192,13 @@
           <t>Change In Other Working Capital</t>
         </is>
       </c>
-      <c r="B38" s="29" t="n">
+      <c r="B38" s="25" t="n">
         <v>31</v>
       </c>
-      <c r="C38" s="29" t="n">
+      <c r="C38" s="25" t="n">
         <v>-106</v>
       </c>
-      <c r="D38" s="29" t="n">
+      <c r="D38" s="25" t="n">
         <v>-224</v>
       </c>
     </row>
@@ -2211,13 +2208,13 @@
           <t>Change In Payables And Accrued Expense</t>
         </is>
       </c>
-      <c r="B39" s="29" t="n">
+      <c r="B39" s="25" t="n">
         <v>-307</v>
       </c>
-      <c r="C39" s="29" t="n">
+      <c r="C39" s="25" t="n">
         <v>101</v>
       </c>
-      <c r="D39" s="29" t="n">
+      <c r="D39" s="25" t="n">
         <v>104</v>
       </c>
     </row>
@@ -2227,13 +2224,13 @@
           <t>Change In Accrued Expense</t>
         </is>
       </c>
-      <c r="B40" s="29" t="n">
+      <c r="B40" s="25" t="n">
         <v>-160</v>
       </c>
-      <c r="C40" s="29" t="n">
+      <c r="C40" s="25" t="n">
         <v>48</v>
       </c>
-      <c r="D40" s="29" t="n">
+      <c r="D40" s="25" t="n">
         <v>34</v>
       </c>
     </row>
@@ -2243,13 +2240,13 @@
           <t>Change In Payable</t>
         </is>
       </c>
-      <c r="B41" s="29" t="n">
+      <c r="B41" s="25" t="n">
         <v>-147</v>
       </c>
-      <c r="C41" s="29" t="n">
+      <c r="C41" s="25" t="n">
         <v>53</v>
       </c>
-      <c r="D41" s="29" t="n">
+      <c r="D41" s="25" t="n">
         <v>70</v>
       </c>
     </row>
@@ -2259,13 +2256,13 @@
           <t>Change In Account Payable</t>
         </is>
       </c>
-      <c r="B42" s="29" t="n">
+      <c r="B42" s="25" t="n">
         <v>-147</v>
       </c>
-      <c r="C42" s="29" t="n">
+      <c r="C42" s="25" t="n">
         <v>53</v>
       </c>
-      <c r="D42" s="29" t="n">
+      <c r="D42" s="25" t="n">
         <v>70</v>
       </c>
     </row>
@@ -2275,13 +2272,13 @@
           <t>Change In Inventory</t>
         </is>
       </c>
-      <c r="B43" s="29" t="n">
+      <c r="B43" s="25" t="n">
         <v>-277</v>
       </c>
-      <c r="C43" s="29" t="n">
+      <c r="C43" s="25" t="n">
         <v>314</v>
       </c>
-      <c r="D43" s="29" t="n">
+      <c r="D43" s="25" t="n">
         <v>-160</v>
       </c>
     </row>
@@ -2291,13 +2288,13 @@
           <t>Change In Receivables</t>
         </is>
       </c>
-      <c r="B44" s="29" t="n">
+      <c r="B44" s="25" t="n">
         <v>750</v>
       </c>
-      <c r="C44" s="29" t="n">
+      <c r="C44" s="25" t="n">
         <v>-395</v>
       </c>
-      <c r="D44" s="29" t="n">
+      <c r="D44" s="25" t="n">
         <v>-100</v>
       </c>
     </row>
@@ -2307,13 +2304,13 @@
           <t>Changes In Account Receivables</t>
         </is>
       </c>
-      <c r="B45" s="29" t="n">
+      <c r="B45" s="25" t="n">
         <v>750</v>
       </c>
-      <c r="C45" s="29" t="n">
+      <c r="C45" s="25" t="n">
         <v>-395</v>
       </c>
-      <c r="D45" s="29" t="n">
+      <c r="D45" s="25" t="n">
         <v>-100</v>
       </c>
     </row>
@@ -2323,13 +2320,13 @@
           <t>Other Non Cash Items</t>
         </is>
       </c>
-      <c r="B46" s="29" t="n">
+      <c r="B46" s="25" t="n">
         <v>114</v>
       </c>
-      <c r="C46" s="29" t="n">
+      <c r="C46" s="25" t="n">
         <v>87</v>
       </c>
-      <c r="D46" s="29" t="n">
+      <c r="D46" s="25" t="n">
         <v>-73</v>
       </c>
     </row>
@@ -2339,13 +2336,13 @@
           <t>Stock Based Compensation</t>
         </is>
       </c>
-      <c r="B47" s="29" t="n">
+      <c r="B47" s="25" t="n">
         <v>165</v>
       </c>
-      <c r="C47" s="29" t="n">
+      <c r="C47" s="25" t="n">
         <v>149</v>
       </c>
-      <c r="D47" s="29" t="n">
+      <c r="D47" s="25" t="n">
         <v>182</v>
       </c>
     </row>
@@ -2355,13 +2352,13 @@
           <t>Asset Impairment Charge</t>
         </is>
       </c>
-      <c r="B48" s="29" t="n">
+      <c r="B48" s="25" t="n">
         <v>672</v>
       </c>
-      <c r="C48" s="29" t="n">
+      <c r="C48" s="25" t="n">
         <v>4</v>
       </c>
-      <c r="D48" s="29" t="n">
+      <c r="D48" s="25" t="n">
         <v>1831</v>
       </c>
     </row>
@@ -2371,13 +2368,13 @@
           <t>Deferred Tax</t>
         </is>
       </c>
-      <c r="B49" s="29" t="n">
+      <c r="B49" s="25" t="n">
         <v>-81</v>
       </c>
-      <c r="C49" s="29" t="n">
+      <c r="C49" s="25" t="n">
         <v>-16</v>
       </c>
-      <c r="D49" s="29" t="n">
+      <c r="D49" s="25" t="n">
         <v>-12</v>
       </c>
     </row>
@@ -2387,13 +2384,13 @@
           <t>Deferred Income Tax</t>
         </is>
       </c>
-      <c r="B50" s="29" t="n">
+      <c r="B50" s="25" t="n">
         <v>-81</v>
       </c>
-      <c r="C50" s="29" t="n">
+      <c r="C50" s="25" t="n">
         <v>-16</v>
       </c>
-      <c r="D50" s="29" t="n">
+      <c r="D50" s="25" t="n">
         <v>-12</v>
       </c>
     </row>
@@ -2403,13 +2400,13 @@
           <t>Depreciation Amortization Depletion</t>
         </is>
       </c>
-      <c r="B51" s="29" t="n">
+      <c r="B51" s="25" t="n">
         <v>448</v>
       </c>
-      <c r="C51" s="29" t="n">
+      <c r="C51" s="25" t="n">
         <v>224</v>
       </c>
-      <c r="D51" s="29" t="n">
+      <c r="D51" s="25" t="n">
         <v>163</v>
       </c>
     </row>
@@ -2419,13 +2416,13 @@
           <t>Depreciation And Amortization</t>
         </is>
       </c>
-      <c r="B52" s="29" t="n">
+      <c r="B52" s="25" t="n">
         <v>448</v>
       </c>
-      <c r="C52" s="29" t="n">
+      <c r="C52" s="25" t="n">
         <v>224</v>
       </c>
-      <c r="D52" s="29" t="n">
+      <c r="D52" s="25" t="n">
         <v>163</v>
       </c>
     </row>
@@ -2435,7 +2432,7 @@
           <t>Amortization Cash Flow</t>
         </is>
       </c>
-      <c r="B53" s="29" t="n">
+      <c r="B53" s="25" t="n">
         <v>133</v>
       </c>
     </row>
@@ -2445,7 +2442,7 @@
           <t>Amortization Of Intangibles</t>
         </is>
       </c>
-      <c r="B54" s="29" t="n">
+      <c r="B54" s="25" t="n">
         <v>133</v>
       </c>
     </row>
@@ -2455,13 +2452,13 @@
           <t>Depreciation</t>
         </is>
       </c>
-      <c r="B55" s="29" t="n">
+      <c r="B55" s="25" t="n">
         <v>315</v>
       </c>
-      <c r="C55" s="29" t="n">
+      <c r="C55" s="25" t="n">
         <v>224</v>
       </c>
-      <c r="D55" s="29" t="n">
+      <c r="D55" s="25" t="n">
         <v>163</v>
       </c>
     </row>
@@ -2471,13 +2468,13 @@
           <t>Operating Gains Losses</t>
         </is>
       </c>
-      <c r="B56" s="29" t="n">
+      <c r="B56" s="25" t="n">
         <v>-85</v>
       </c>
-      <c r="C56" s="29" t="n">
+      <c r="C56" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="D56" s="29" t="n">
+      <c r="D56" s="25" t="n">
         <v>14</v>
       </c>
     </row>
@@ -2487,13 +2484,13 @@
           <t>Earnings Losses From Equity Investments</t>
         </is>
       </c>
-      <c r="B57" s="29" t="n">
+      <c r="B57" s="25" t="n">
         <v>-45</v>
       </c>
-      <c r="C57" s="29" t="n">
+      <c r="C57" s="25" t="n">
         <v>49</v>
       </c>
-      <c r="D57" s="29" t="n">
+      <c r="D57" s="25" t="n">
         <v>74</v>
       </c>
     </row>
@@ -2503,10 +2500,10 @@
           <t>Gain Loss On Investment Securities</t>
         </is>
       </c>
-      <c r="B58" s="29" t="n">
+      <c r="B58" s="25" t="n">
         <v>-3</v>
       </c>
-      <c r="C58" s="29" t="n">
+      <c r="C58" s="25" t="n">
         <v>-1</v>
       </c>
     </row>
@@ -2516,13 +2513,13 @@
           <t>Net Foreign Currency Exchange Gain Loss</t>
         </is>
       </c>
-      <c r="B59" s="29" t="n">
+      <c r="B59" s="25" t="n">
         <v>-37</v>
       </c>
-      <c r="C59" s="29" t="n">
+      <c r="C59" s="25" t="n">
         <v>13</v>
       </c>
-      <c r="D59" s="29" t="n">
+      <c r="D59" s="25" t="n">
         <v>-25</v>
       </c>
     </row>
@@ -2532,13 +2529,13 @@
           <t>Gain Loss On Sale Of Business</t>
         </is>
       </c>
-      <c r="B60" s="29" t="n">
+      <c r="B60" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="C60" s="29" t="n">
+      <c r="C60" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="D60" s="29" t="n">
+      <c r="D60" s="25" t="n">
         <v>-34</v>
       </c>
     </row>
@@ -2548,13 +2545,13 @@
           <t>Net Income From Continuing Operations</t>
         </is>
       </c>
-      <c r="B61" s="29" t="n">
+      <c r="B61" s="25" t="n">
         <v>-2143</v>
       </c>
-      <c r="C61" s="29" t="n">
+      <c r="C61" s="25" t="n">
         <v>-672</v>
       </c>
-      <c r="D61" s="29" t="n">
+      <c r="D61" s="25" t="n">
         <v>-1641</v>
       </c>
     </row>
@@ -2564,6 +2561,292 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="38" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>SNDK — 12-month price target (lens triangulation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Blue = inputs (weights, Ke, dividends, Street weight); black = live formulas. Change a weight and the blended fair value and target recalculate. Guardrail exclusions are already reflected in the effective weights.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="9" t="inlineStr">
+        <is>
+          <t>Lens</t>
+        </is>
+      </c>
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="C4" s="10" t="inlineStr">
+        <is>
+          <t>Value / share</t>
+        </is>
+      </c>
+      <c r="D4" s="10" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E4" s="10" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F4" s="10" t="inlineStr">
+        <is>
+          <t>Weight</t>
+        </is>
+      </c>
+      <c r="G4" s="10" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Discounted cash flow (FCFF)</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>intrinsic</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>497.0336741547966</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>399.777015638166</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>609.0982264335238</v>
+      </c>
+      <c r="F5" s="11" t="n">
+        <v>0.2028985507246377</v>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>ok — down-weighted: 0.4x the median of the other lenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Forward P/E</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>relative</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>1387.821099384215</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>1138.013301495057</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>1637.628897273374</v>
+      </c>
+      <c r="F6" s="11" t="n">
+        <v>0.4347826086956522</v>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Forward EV/EBITDA</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>relative</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>1164.912487830058</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>954.5463562674171</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>1375.278619392698</v>
+      </c>
+      <c r="F7" s="11" t="n">
+        <v>0.3623188405797102</v>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>Weights sum</t>
+        </is>
+      </c>
+      <c r="B9" s="12">
+        <f>SUM(F5:F7)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="13" t="inlineStr">
+        <is>
+          <t>Blended fair value (today)</t>
+        </is>
+      </c>
+      <c r="B10" s="14">
+        <f>SUMPRODUCT(C5:C7,F5:F7)/SUM(F5:F7)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Cost of equity (Ke)</t>
+        </is>
+      </c>
+      <c r="B11" s="15" t="n">
+        <v>0.0939029736745141</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Dividends per share (12m)</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Model 12-month target = FV×(1+Ke)−DPS</t>
+        </is>
+      </c>
+      <c r="B13" s="16">
+        <f>$B$10*(1+$B$11)-$B$12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Street mean target</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="n">
+        <v>1975.95</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Street weight in target</t>
+        </is>
+      </c>
+      <c r="B15" s="11" t="n">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="13" t="inlineStr">
+        <is>
+          <t>Published 12-month target</t>
+        </is>
+      </c>
+      <c r="B16" s="17">
+        <f>(1-$B$15)*$B$13+$B$15*$B$14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>Current price</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="n">
+        <v>1727.18</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>Engine target (incl. plausibility band)</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="n">
+        <v>1343.662376005138</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="8" t="inlineStr">
+        <is>
+          <t>Guardrails</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>Discounted cash flow (FCFF) sits 0.4x the lens median and was down-weighted by 60%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Target anchored 15% to the Street consensus ($1,975.95); model-only target $1,232.08.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2588,14 +2871,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>SNDK — projected P&amp;L &amp; levered FCF (analyst-driven)</t>
+          <t>SNDK — projected P&amp;L &amp; levered FCF (DCF base case)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Blue = analyst estimates; black = live formulas. The Levered FCF row is the exact cash flow discounted on the 'SWS Valuation' sheet — P&amp;L, cash flow and fair value are one reconciled chain.</t>
+          <t>Blue = consensus-sourced figures; black = live formulas. Revenue and EBIT margin are the DCF base-case drivers; levered FCF = unlevered FCF less after-tax interest.</t>
         </is>
       </c>
     </row>
@@ -2657,40 +2940,40 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="11" t="inlineStr">
+      <c r="A5" s="13" t="inlineStr">
         <is>
           <t>Revenue (mn)</t>
         </is>
       </c>
-      <c r="B5" s="12" t="n">
-        <v>19771.04654</v>
-      </c>
-      <c r="C5" s="12" t="n">
-        <v>48134.92875</v>
-      </c>
-      <c r="D5" s="13" t="n">
-        <v>49578.9766125</v>
-      </c>
-      <c r="E5" s="13" t="n">
-        <v>51066.345910875</v>
-      </c>
-      <c r="F5" s="13" t="n">
-        <v>52598.33628820125</v>
-      </c>
-      <c r="G5" s="13" t="n">
-        <v>54176.28637684729</v>
-      </c>
-      <c r="H5" s="13" t="n">
-        <v>55801.57496815271</v>
-      </c>
-      <c r="I5" s="13" t="n">
-        <v>57475.6222171973</v>
-      </c>
-      <c r="J5" s="13" t="n">
-        <v>59199.89088371322</v>
-      </c>
-      <c r="K5" s="13" t="n">
-        <v>60975.88761022461</v>
+      <c r="B5" s="18" t="n">
+        <v>19770</v>
+      </c>
+      <c r="C5" s="18" t="n">
+        <v>48130</v>
+      </c>
+      <c r="D5" s="19" t="n">
+        <v>52146.48516853159</v>
+      </c>
+      <c r="E5" s="19" t="n">
+        <v>55546.12408119863</v>
+      </c>
+      <c r="F5" s="19" t="n">
+        <v>58470.05309974719</v>
+      </c>
+      <c r="G5" s="19" t="n">
+        <v>61043.12004096285</v>
+      </c>
+      <c r="H5" s="19" t="n">
+        <v>63367.03086927003</v>
+      </c>
+      <c r="I5" s="19" t="n">
+        <v>65520.72769967289</v>
+      </c>
+      <c r="J5" s="19" t="n">
+        <v>67563.6912192493</v>
+      </c>
+      <c r="K5" s="19" t="n">
+        <v>69252.78349973053</v>
       </c>
     </row>
     <row r="6">
@@ -2704,39 +2987,39 @@
           <t>—</t>
         </is>
       </c>
-      <c r="C6" s="14">
+      <c r="C6" s="12">
         <f>C5/B5-1</f>
         <v/>
       </c>
-      <c r="D6" s="14">
+      <c r="D6" s="12">
         <f>D5/C5-1</f>
         <v/>
       </c>
-      <c r="E6" s="14">
+      <c r="E6" s="12">
         <f>E5/D5-1</f>
         <v/>
       </c>
-      <c r="F6" s="14">
+      <c r="F6" s="12">
         <f>F5/E5-1</f>
         <v/>
       </c>
-      <c r="G6" s="14">
+      <c r="G6" s="12">
         <f>G5/F5-1</f>
         <v/>
       </c>
-      <c r="H6" s="14">
+      <c r="H6" s="12">
         <f>H5/G5-1</f>
         <v/>
       </c>
-      <c r="I6" s="14">
+      <c r="I6" s="12">
         <f>I5/H5-1</f>
         <v/>
       </c>
-      <c r="J6" s="14">
+      <c r="J6" s="12">
         <f>J5/I5-1</f>
         <v/>
       </c>
-      <c r="K6" s="14">
+      <c r="K6" s="12">
         <f>K5/J5-1</f>
         <v/>
       </c>
@@ -2747,35 +3030,35 @@
           <t>EBIT margin</t>
         </is>
       </c>
-      <c r="B7" s="15" t="n">
-        <v>0.06893269884432358</v>
-      </c>
-      <c r="C7" s="15" t="n">
-        <v>0.06893269884432358</v>
-      </c>
-      <c r="D7" s="15" t="n">
-        <v>0.06893269884432358</v>
-      </c>
-      <c r="E7" s="15" t="n">
-        <v>0.06893269884432358</v>
-      </c>
-      <c r="F7" s="15" t="n">
-        <v>0.06893269884432358</v>
-      </c>
-      <c r="G7" s="15" t="n">
-        <v>0.06893269884432358</v>
-      </c>
-      <c r="H7" s="15" t="n">
-        <v>0.06893269884432358</v>
-      </c>
-      <c r="I7" s="15" t="n">
-        <v>0.06893269884432358</v>
-      </c>
-      <c r="J7" s="15" t="n">
-        <v>0.06893269884432358</v>
-      </c>
-      <c r="K7" s="15" t="n">
-        <v>0.06893269884432358</v>
+      <c r="B7" s="11" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="C7" s="11" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="D7" s="11" t="n">
+        <v>0.3079837537096477</v>
+      </c>
+      <c r="E7" s="11" t="n">
+        <v>0.2659675074192954</v>
+      </c>
+      <c r="F7" s="11" t="n">
+        <v>0.2239512611289431</v>
+      </c>
+      <c r="G7" s="11" t="n">
+        <v>0.1819350148385909</v>
+      </c>
+      <c r="H7" s="11" t="n">
+        <v>0.1399187685482386</v>
+      </c>
+      <c r="I7" s="11" t="n">
+        <v>0.09790252225788632</v>
+      </c>
+      <c r="J7" s="11" t="n">
+        <v>0.09790252225788632</v>
+      </c>
+      <c r="K7" s="11" t="n">
+        <v>0.09790252225788632</v>
       </c>
     </row>
     <row r="8">
@@ -2784,43 +3067,43 @@
           <t>EBIT (mn)</t>
         </is>
       </c>
-      <c r="B8" s="13">
+      <c r="B8" s="19">
         <f>B5*B7</f>
         <v/>
       </c>
-      <c r="C8" s="13">
+      <c r="C8" s="19">
         <f>C5*C7</f>
         <v/>
       </c>
-      <c r="D8" s="13">
+      <c r="D8" s="19">
         <f>D5*D7</f>
         <v/>
       </c>
-      <c r="E8" s="13">
+      <c r="E8" s="19">
         <f>E5*E7</f>
         <v/>
       </c>
-      <c r="F8" s="13">
+      <c r="F8" s="19">
         <f>F5*F7</f>
         <v/>
       </c>
-      <c r="G8" s="13">
+      <c r="G8" s="19">
         <f>G5*G7</f>
         <v/>
       </c>
-      <c r="H8" s="13">
+      <c r="H8" s="19">
         <f>H5*H7</f>
         <v/>
       </c>
-      <c r="I8" s="13">
+      <c r="I8" s="19">
         <f>I5*I7</f>
         <v/>
       </c>
-      <c r="J8" s="13">
+      <c r="J8" s="19">
         <f>J5*J7</f>
         <v/>
       </c>
-      <c r="K8" s="13">
+      <c r="K8" s="19">
         <f>K5*K7</f>
         <v/>
       </c>
@@ -2831,35 +3114,35 @@
           <t>Net income (mn)</t>
         </is>
       </c>
-      <c r="B9" s="12" t="n">
-        <v>9834.067721416541</v>
-      </c>
-      <c r="C9" s="12" t="n">
-        <v>30280.1497618728</v>
-      </c>
-      <c r="D9" s="13" t="n">
-        <v>-11061.7403971601</v>
-      </c>
-      <c r="E9" s="13" t="n">
-        <v>-11393.5926090749</v>
-      </c>
-      <c r="F9" s="13" t="n">
-        <v>-11735.40038734714</v>
-      </c>
-      <c r="G9" s="13" t="n">
-        <v>-12087.46239896756</v>
-      </c>
-      <c r="H9" s="13" t="n">
-        <v>-12450.08627093659</v>
-      </c>
-      <c r="I9" s="13" t="n">
-        <v>-12823.58885906469</v>
-      </c>
-      <c r="J9" s="13" t="n">
-        <v>-13208.29652483663</v>
-      </c>
-      <c r="K9" s="13" t="n">
-        <v>-13604.54542058173</v>
+      <c r="B9" s="18" t="n">
+        <v>9834.640828779999</v>
+      </c>
+      <c r="C9" s="18" t="n">
+        <v>30279.91281826</v>
+      </c>
+      <c r="D9" s="19" t="n">
+        <v>11997.95268372662</v>
+      </c>
+      <c r="E9" s="19" t="n">
+        <v>11032.84812650948</v>
+      </c>
+      <c r="F9" s="19" t="n">
+        <v>9773.581597473492</v>
+      </c>
+      <c r="G9" s="19" t="n">
+        <v>8282.160712834846</v>
+      </c>
+      <c r="H9" s="19" t="n">
+        <v>6602.427694339863</v>
+      </c>
+      <c r="I9" s="19" t="n">
+        <v>4763.7333764776</v>
+      </c>
+      <c r="J9" s="19" t="n">
+        <v>4913.741837563135</v>
+      </c>
+      <c r="K9" s="19" t="n">
+        <v>5037.766633502212</v>
       </c>
     </row>
     <row r="10">
@@ -2910,40 +3193,40 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="11" t="inlineStr">
+      <c r="A12" s="13" t="inlineStr">
         <is>
           <t>Levered FCF (mn)</t>
         </is>
       </c>
-      <c r="B12" s="17" t="n">
-        <v>9834.067721416541</v>
-      </c>
-      <c r="C12" s="17" t="n">
-        <v>30280.1497618728</v>
-      </c>
-      <c r="D12" s="17" t="n">
-        <v>86358.51085594577</v>
-      </c>
-      <c r="E12" s="17" t="n">
-        <v>226679.1076704588</v>
-      </c>
-      <c r="F12" s="17" t="n">
-        <v>543517.1564049842</v>
-      </c>
-      <c r="G12" s="17" t="n">
-        <v>1179766.584637911</v>
-      </c>
-      <c r="H12" s="17" t="n">
-        <v>2292867.079194676</v>
-      </c>
-      <c r="I12" s="17" t="n">
-        <v>3935406.209191163</v>
-      </c>
-      <c r="J12" s="17" t="n">
-        <v>5860788.222412483</v>
-      </c>
-      <c r="K12" s="17" t="n">
-        <v>7397035.812449798</v>
+      <c r="B12" s="20" t="n">
+        <v>3560.552232002623</v>
+      </c>
+      <c r="C12" s="20" t="n">
+        <v>8918.077482256851</v>
+      </c>
+      <c r="D12" s="20" t="n">
+        <v>11900.35014518295</v>
+      </c>
+      <c r="E12" s="20" t="n">
+        <v>10949.38082594039</v>
+      </c>
+      <c r="F12" s="20" t="n">
+        <v>9667.012762287175</v>
+      </c>
+      <c r="G12" s="20" t="n">
+        <v>8120.974262642939</v>
+      </c>
+      <c r="H12" s="20" t="n">
+        <v>6360.818269060845</v>
+      </c>
+      <c r="I12" s="20" t="n">
+        <v>4420.748553466789</v>
+      </c>
+      <c r="J12" s="20" t="n">
+        <v>4452.207158416158</v>
+      </c>
+      <c r="K12" s="20" t="n">
+        <v>4487.321313369473</v>
       </c>
     </row>
     <row r="13">
@@ -2952,43 +3235,43 @@
           <t>FCF margin</t>
         </is>
       </c>
-      <c r="B13" s="14">
+      <c r="B13" s="12">
         <f>B12/B5</f>
         <v/>
       </c>
-      <c r="C13" s="14">
+      <c r="C13" s="12">
         <f>C12/C5</f>
         <v/>
       </c>
-      <c r="D13" s="14">
+      <c r="D13" s="12">
         <f>D12/D5</f>
         <v/>
       </c>
-      <c r="E13" s="14">
+      <c r="E13" s="12">
         <f>E12/E5</f>
         <v/>
       </c>
-      <c r="F13" s="14">
+      <c r="F13" s="12">
         <f>F12/F5</f>
         <v/>
       </c>
-      <c r="G13" s="14">
+      <c r="G13" s="12">
         <f>G12/G5</f>
         <v/>
       </c>
-      <c r="H13" s="14">
+      <c r="H13" s="12">
         <f>H12/H5</f>
         <v/>
       </c>
-      <c r="I13" s="14">
+      <c r="I13" s="12">
         <f>I12/I5</f>
         <v/>
       </c>
-      <c r="J13" s="14">
+      <c r="J13" s="12">
         <f>J12/J5</f>
         <v/>
       </c>
-      <c r="K13" s="14">
+      <c r="K13" s="12">
         <f>K12/K5</f>
         <v/>
       </c>
@@ -2996,438 +3279,8 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>→ These Levered FCF figures feed the DCF on the 'SWS Valuation' sheet.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E34"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>SNDK — 2-Stage Free Cash Flow to Equity</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Simply Wall St methodology. Blue = analyst inputs you can change; black = live formulas. Discounted at the cost of equity. Every figure is traceable; change a blue cell and the model recalculates.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="8" t="inlineStr">
-        <is>
-          <t>Cost of equity</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>Risk-free rate</t>
-        </is>
-      </c>
-      <c r="B5" s="18" t="n">
-        <v>0.036</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>Equity risk premium</t>
-        </is>
-      </c>
-      <c r="B6" s="18" t="n">
-        <v>0.046</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>Levered beta (clamped 0.8–2.0)</t>
-        </is>
-      </c>
-      <c r="B7" s="19" t="n">
-        <v>1.207</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>Cost of equity = Rf + β·ERP</t>
-        </is>
-      </c>
-      <c r="B8" s="20">
-        <f>$B$5+$B$7*$B$6</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>Perpetual growth (g)</t>
-        </is>
-      </c>
-      <c r="B10" s="18" t="n">
-        <v>0.025</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>Shares outstanding (mn)</t>
-        </is>
-      </c>
-      <c r="B11" s="12" t="n">
-        <v>148.089758</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="8" t="inlineStr">
-        <is>
-          <t>Stage 1 — 10-year cash-flow forecast</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="9" t="inlineStr">
-        <is>
-          <t>Year</t>
-        </is>
-      </c>
-      <c r="B14" s="10" t="inlineStr">
-        <is>
-          <t>Cash flow (mn)</t>
-        </is>
-      </c>
-      <c r="C14" s="10" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="D14" s="10" t="inlineStr">
-        <is>
-          <t>Discount factor</t>
-        </is>
-      </c>
-      <c r="E14" s="10" t="inlineStr">
-        <is>
-          <t>PV (mn)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="21" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B15" s="12" t="n">
-        <v>9834.067721416541</v>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>Analyst</t>
-        </is>
-      </c>
-      <c r="D15" s="22">
-        <f>1/(1+$B$8)^1</f>
-        <v/>
-      </c>
-      <c r="E15" s="13">
-        <f>B15*D15</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="21" t="n">
-        <v>2027</v>
-      </c>
-      <c r="B16" s="12" t="n">
-        <v>30280.1497618728</v>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>Analyst</t>
-        </is>
-      </c>
-      <c r="D16" s="22">
-        <f>1/(1+$B$8)^2</f>
-        <v/>
-      </c>
-      <c r="E16" s="13">
-        <f>B16*D16</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="21" t="n">
-        <v>2028</v>
-      </c>
-      <c r="B17" s="12" t="n">
-        <v>86358.51085594577</v>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>Analyst</t>
-        </is>
-      </c>
-      <c r="D17" s="22">
-        <f>1/(1+$B$8)^3</f>
-        <v/>
-      </c>
-      <c r="E17" s="13">
-        <f>B17*D17</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="21" t="n">
-        <v>2029</v>
-      </c>
-      <c r="B18" s="12" t="n">
-        <v>226679.1076704588</v>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>Analyst</t>
-        </is>
-      </c>
-      <c r="D18" s="22">
-        <f>1/(1+$B$8)^4</f>
-        <v/>
-      </c>
-      <c r="E18" s="13">
-        <f>B18*D18</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="21" t="n">
-        <v>2030</v>
-      </c>
-      <c r="B19" s="12" t="n">
-        <v>543517.1564049842</v>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>Analyst</t>
-        </is>
-      </c>
-      <c r="D19" s="22">
-        <f>1/(1+$B$8)^5</f>
-        <v/>
-      </c>
-      <c r="E19" s="13">
-        <f>B19*D19</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="21" t="n">
-        <v>2031</v>
-      </c>
-      <c r="B20" s="12" t="n">
-        <v>1179766.584637911</v>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>Analyst</t>
-        </is>
-      </c>
-      <c r="D20" s="22">
-        <f>1/(1+$B$8)^6</f>
-        <v/>
-      </c>
-      <c r="E20" s="13">
-        <f>B20*D20</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="21" t="n">
-        <v>2032</v>
-      </c>
-      <c r="B21" s="12" t="n">
-        <v>2292867.079194676</v>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>Analyst</t>
-        </is>
-      </c>
-      <c r="D21" s="22">
-        <f>1/(1+$B$8)^7</f>
-        <v/>
-      </c>
-      <c r="E21" s="13">
-        <f>B21*D21</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="21" t="n">
-        <v>2033</v>
-      </c>
-      <c r="B22" s="12" t="n">
-        <v>3935406.209191163</v>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>Analyst</t>
-        </is>
-      </c>
-      <c r="D22" s="22">
-        <f>1/(1+$B$8)^8</f>
-        <v/>
-      </c>
-      <c r="E22" s="13">
-        <f>B22*D22</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="21" t="n">
-        <v>2034</v>
-      </c>
-      <c r="B23" s="12" t="n">
-        <v>5860788.222412483</v>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>Analyst</t>
-        </is>
-      </c>
-      <c r="D23" s="22">
-        <f>1/(1+$B$8)^9</f>
-        <v/>
-      </c>
-      <c r="E23" s="13">
-        <f>B23*D23</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="21" t="n">
-        <v>2035</v>
-      </c>
-      <c r="B24" s="12" t="n">
-        <v>7397035.812449798</v>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>Analyst</t>
-        </is>
-      </c>
-      <c r="D24" s="22">
-        <f>1/(1+$B$8)^10</f>
-        <v/>
-      </c>
-      <c r="E24" s="13">
-        <f>B24*D24</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="11" t="inlineStr">
-        <is>
-          <t>PV of next 10 years' cash flows</t>
-        </is>
-      </c>
-      <c r="B25" s="23">
-        <f>SUM(E15:E24)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="8" t="inlineStr">
-        <is>
-          <t>Stage 2 — terminal value</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="3" t="inlineStr">
-        <is>
-          <t>Terminal value = CFn·(1+g)/(Ke−g)</t>
-        </is>
-      </c>
-      <c r="B28" s="13">
-        <f>B24*(1+$B$10)/($B$8-$B$10)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="3" t="inlineStr">
-        <is>
-          <t>PV of terminal value</t>
-        </is>
-      </c>
-      <c r="B29" s="13">
-        <f>$B$28/(1+$B$8)^10</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="11" t="inlineStr">
-        <is>
-          <t>Total equity value</t>
-        </is>
-      </c>
-      <c r="B31" s="23">
-        <f>$B$25+$B$29</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="11" t="inlineStr">
-        <is>
-          <t>Value per share</t>
-        </is>
-      </c>
-      <c r="B32" s="24">
-        <f>$B$31/$B$11</f>
-        <v/>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="3" t="inlineStr">
-        <is>
-          <t>Current price</t>
-        </is>
-      </c>
-      <c r="B33" s="6" t="n">
-        <v>1727.18</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="3" t="inlineStr">
-        <is>
-          <t>Upside / (downside)</t>
-        </is>
-      </c>
-      <c r="B34" s="14">
-        <f>B32/$B$33-1</f>
-        <v/>
+          <t>→ Unlevered FCF (before interest) is what the 'DCF' sheet discounts.</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -3441,7 +3294,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F30"/>
+  <dimension ref="A1:K30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -3467,7 +3320,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Blue cells are inputs — change them and the whole model recalculates. Source: yfinance, retrieved 2026-07-09.</t>
+          <t>Blue cells are inputs — change them and the whole model recalculates. Source: Yahoo snapshot as of 2026-07-09, retrieved 2026-10-13.</t>
         </is>
       </c>
     </row>
@@ -3494,7 +3347,7 @@
           <t>Diluted shares (mn)</t>
         </is>
       </c>
-      <c r="B6" s="12" t="n">
+      <c r="B6" s="18" t="n">
         <v>148.089758</v>
       </c>
     </row>
@@ -3504,7 +3357,7 @@
           <t>Total debt (USDmm)</t>
         </is>
       </c>
-      <c r="B7" s="12" t="n">
+      <c r="B7" s="18" t="n">
         <v>2042</v>
       </c>
     </row>
@@ -3514,7 +3367,7 @@
           <t>Cash &amp; ST investments (USDmm)</t>
         </is>
       </c>
-      <c r="B8" s="12" t="n">
+      <c r="B8" s="18" t="n">
         <v>1481</v>
       </c>
     </row>
@@ -3524,7 +3377,7 @@
           <t>Minority interest (USDmm)</t>
         </is>
       </c>
-      <c r="B9" s="12" t="n">
+      <c r="B9" s="18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3534,7 +3387,7 @@
           <t>Net debt (USDmm)</t>
         </is>
       </c>
-      <c r="B10" s="13">
+      <c r="B10" s="19">
         <f>Assumptions!$B$7-Assumptions!$B$8</f>
         <v/>
       </c>
@@ -3552,7 +3405,7 @@
           <t>Risk-free rate (Rf)</t>
         </is>
       </c>
-      <c r="B13" s="25" t="n">
+      <c r="B13" s="21" t="n">
         <v>0.043</v>
       </c>
     </row>
@@ -3562,7 +3415,7 @@
           <t>Equity risk premium (ERP)</t>
         </is>
       </c>
-      <c r="B14" s="25" t="n">
+      <c r="B14" s="21" t="n">
         <v>0.046</v>
       </c>
     </row>
@@ -3572,7 +3425,7 @@
           <t>Country risk premium</t>
         </is>
       </c>
-      <c r="B15" s="18" t="n">
+      <c r="B15" s="15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3582,7 +3435,7 @@
           <t>Size premium</t>
         </is>
       </c>
-      <c r="B16" s="18" t="n">
+      <c r="B16" s="15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3592,8 +3445,8 @@
           <t>Beta (levered)</t>
         </is>
       </c>
-      <c r="B17" s="26" t="n">
-        <v>1</v>
+      <c r="B17" s="22" t="n">
+        <v>1.11</v>
       </c>
     </row>
     <row r="18">
@@ -3602,7 +3455,7 @@
           <t>Pre-tax cost of debt</t>
         </is>
       </c>
-      <c r="B18" s="18" t="n">
+      <c r="B18" s="15" t="n">
         <v>0.051</v>
       </c>
     </row>
@@ -3612,7 +3465,7 @@
           <t>Tax rate</t>
         </is>
       </c>
-      <c r="B19" s="15" t="n">
+      <c r="B19" s="11" t="n">
         <v>0.25</v>
       </c>
     </row>
@@ -3629,7 +3482,7 @@
           <t>Terminal growth (g)</t>
         </is>
       </c>
-      <c r="B22" s="25" t="n">
+      <c r="B22" s="21" t="n">
         <v>0.025</v>
       </c>
     </row>
@@ -3671,6 +3524,31 @@
           <t>FY2030E</t>
         </is>
       </c>
+      <c r="G25" s="10" t="inlineStr">
+        <is>
+          <t>FY2031E</t>
+        </is>
+      </c>
+      <c r="H25" s="10" t="inlineStr">
+        <is>
+          <t>FY2032E</t>
+        </is>
+      </c>
+      <c r="I25" s="10" t="inlineStr">
+        <is>
+          <t>FY2033E</t>
+        </is>
+      </c>
+      <c r="J25" s="10" t="inlineStr">
+        <is>
+          <t>FY2034E</t>
+        </is>
+      </c>
+      <c r="K25" s="10" t="inlineStr">
+        <is>
+          <t>FY2035E</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
@@ -3678,20 +3556,35 @@
           <t>Revenue growth</t>
         </is>
       </c>
-      <c r="B26" s="15" t="n">
-        <v>0.09932312697218015</v>
-      </c>
-      <c r="C26" s="15" t="n">
-        <v>0.08074234522913512</v>
-      </c>
-      <c r="D26" s="15" t="n">
-        <v>0.06216156348609007</v>
-      </c>
-      <c r="E26" s="15" t="n">
-        <v>0.04358078174304503</v>
-      </c>
-      <c r="F26" s="15" t="n">
-        <v>0.02499999999999999</v>
+      <c r="B26" s="11" t="n">
+        <v>1.687967369136642</v>
+      </c>
+      <c r="C26" s="11" t="n">
+        <v>1.434496712190187</v>
+      </c>
+      <c r="D26" s="11" t="n">
+        <v>0.08345076186435872</v>
+      </c>
+      <c r="E26" s="11" t="n">
+        <v>0.06519401838263497</v>
+      </c>
+      <c r="F26" s="11" t="n">
+        <v>0.05263965878653004</v>
+      </c>
+      <c r="G26" s="11" t="n">
+        <v>0.04400657780874821</v>
+      </c>
+      <c r="H26" s="11" t="n">
+        <v>0.03806998768653584</v>
+      </c>
+      <c r="I26" s="11" t="n">
+        <v>0.0339876557392448</v>
+      </c>
+      <c r="J26" s="11" t="n">
+        <v>0.03118041559215805</v>
+      </c>
+      <c r="K26" s="11" t="n">
+        <v>0.025</v>
       </c>
     </row>
     <row r="27">
@@ -3700,20 +3593,35 @@
           <t>EBIT margin</t>
         </is>
       </c>
-      <c r="B27" s="15" t="n">
-        <v>0.06893269884432358</v>
-      </c>
-      <c r="C27" s="15" t="n">
-        <v>0.05502318266953895</v>
-      </c>
-      <c r="D27" s="15" t="n">
-        <v>0.04111366649475431</v>
-      </c>
-      <c r="E27" s="15" t="n">
-        <v>0.02720415031996967</v>
-      </c>
-      <c r="F27" s="15" t="n">
-        <v>0.01329463414518504</v>
+      <c r="B27" s="11" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="C27" s="11" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="D27" s="11" t="n">
+        <v>0.3079837537096477</v>
+      </c>
+      <c r="E27" s="11" t="n">
+        <v>0.2659675074192954</v>
+      </c>
+      <c r="F27" s="11" t="n">
+        <v>0.2239512611289431</v>
+      </c>
+      <c r="G27" s="11" t="n">
+        <v>0.1819350148385909</v>
+      </c>
+      <c r="H27" s="11" t="n">
+        <v>0.1399187685482386</v>
+      </c>
+      <c r="I27" s="11" t="n">
+        <v>0.09790252225788632</v>
+      </c>
+      <c r="J27" s="11" t="n">
+        <v>0.09790252225788632</v>
+      </c>
+      <c r="K27" s="11" t="n">
+        <v>0.09790252225788632</v>
       </c>
     </row>
     <row r="28">
@@ -3722,19 +3630,34 @@
           <t>D&amp;A % of revenue</t>
         </is>
       </c>
-      <c r="B28" s="15" t="n">
+      <c r="B28" s="11" t="n">
         <v>0.04313061746637292</v>
       </c>
-      <c r="C28" s="15" t="n">
+      <c r="C28" s="11" t="n">
         <v>0.04313061746637292</v>
       </c>
-      <c r="D28" s="15" t="n">
+      <c r="D28" s="11" t="n">
         <v>0.04313061746637292</v>
       </c>
-      <c r="E28" s="15" t="n">
+      <c r="E28" s="11" t="n">
         <v>0.04313061746637292</v>
       </c>
-      <c r="F28" s="15" t="n">
+      <c r="F28" s="11" t="n">
+        <v>0.04313061746637292</v>
+      </c>
+      <c r="G28" s="11" t="n">
+        <v>0.04313061746637292</v>
+      </c>
+      <c r="H28" s="11" t="n">
+        <v>0.04313061746637292</v>
+      </c>
+      <c r="I28" s="11" t="n">
+        <v>0.04313061746637292</v>
+      </c>
+      <c r="J28" s="11" t="n">
+        <v>0.04313061746637292</v>
+      </c>
+      <c r="K28" s="11" t="n">
         <v>0.04313061746637292</v>
       </c>
     </row>
@@ -3744,20 +3667,35 @@
           <t>Capex % of revenue</t>
         </is>
       </c>
-      <c r="B29" s="15" t="n">
+      <c r="B29" s="11" t="n">
         <v>0.02954472082786249</v>
       </c>
-      <c r="C29" s="15" t="n">
-        <v>0.02954472082786249</v>
-      </c>
-      <c r="D29" s="15" t="n">
-        <v>0.02954472082786249</v>
-      </c>
-      <c r="E29" s="15" t="n">
-        <v>0.02954472082786249</v>
-      </c>
-      <c r="F29" s="15" t="n">
-        <v>0.02954472082786249</v>
+      <c r="C29" s="11" t="n">
+        <v>0.03153349398176779</v>
+      </c>
+      <c r="D29" s="11" t="n">
+        <v>0.03352226713567309</v>
+      </c>
+      <c r="E29" s="11" t="n">
+        <v>0.0355110402895784</v>
+      </c>
+      <c r="F29" s="11" t="n">
+        <v>0.0374998134434837</v>
+      </c>
+      <c r="G29" s="11" t="n">
+        <v>0.039488586597389</v>
+      </c>
+      <c r="H29" s="11" t="n">
+        <v>0.0414773597512943</v>
+      </c>
+      <c r="I29" s="11" t="n">
+        <v>0.04346613290519961</v>
+      </c>
+      <c r="J29" s="11" t="n">
+        <v>0.0454549060591049</v>
+      </c>
+      <c r="K29" s="11" t="n">
+        <v>0.04744367921301021</v>
       </c>
     </row>
     <row r="30">
@@ -3766,7 +3704,7 @@
           <t>ΔNWC % of Δrevenue</t>
         </is>
       </c>
-      <c r="B30" s="15" t="n">
+      <c r="B30" s="11" t="n">
         <v>0.1490467937608319</v>
       </c>
     </row>
@@ -3830,7 +3768,7 @@
           <t>Market value of equity (mm)</t>
         </is>
       </c>
-      <c r="B6" s="27">
+      <c r="B6" s="23">
         <f>Assumptions!$B$5*Assumptions!$B$6</f>
         <v/>
       </c>
@@ -3841,7 +3779,7 @@
           <t>Debt (book, mm)</t>
         </is>
       </c>
-      <c r="B7" s="27">
+      <c r="B7" s="23">
         <f>Assumptions!$B$7</f>
         <v/>
       </c>
@@ -3852,7 +3790,7 @@
           <t>Weight of equity</t>
         </is>
       </c>
-      <c r="B8" s="14">
+      <c r="B8" s="12">
         <f>WACC!$B$6/(WACC!$B$6+WACC!$B$7)</f>
         <v/>
       </c>
@@ -3863,18 +3801,18 @@
           <t>Weight of debt</t>
         </is>
       </c>
-      <c r="B9" s="14">
+      <c r="B9" s="12">
         <f>1-WACC!$B$8</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="11" t="inlineStr">
+      <c r="A10" s="13" t="inlineStr">
         <is>
           <t>WACC</t>
         </is>
       </c>
-      <c r="B10" s="28">
+      <c r="B10" s="24">
         <f>WACC!$B$8*WACC!$B$4+WACC!$B$9*WACC!$B$5</f>
         <v/>
       </c>
@@ -3890,7 +3828,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:N14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -3902,6 +3840,11 @@
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3964,6 +3907,31 @@
           <t>FY2030E</t>
         </is>
       </c>
+      <c r="J4" s="10" t="inlineStr">
+        <is>
+          <t>FY2031E</t>
+        </is>
+      </c>
+      <c r="K4" s="10" t="inlineStr">
+        <is>
+          <t>FY2032E</t>
+        </is>
+      </c>
+      <c r="L4" s="10" t="inlineStr">
+        <is>
+          <t>FY2033E</t>
+        </is>
+      </c>
+      <c r="M4" s="10" t="inlineStr">
+        <is>
+          <t>FY2034E</t>
+        </is>
+      </c>
+      <c r="N4" s="10" t="inlineStr">
+        <is>
+          <t>FY2035E</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -3971,33 +3939,53 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B5" s="29" t="n">
+      <c r="B5" s="25" t="n">
         <v>6086</v>
       </c>
-      <c r="C5" s="29" t="n">
+      <c r="C5" s="25" t="n">
         <v>6663</v>
       </c>
-      <c r="D5" s="29" t="n">
+      <c r="D5" s="25" t="n">
         <v>7355</v>
       </c>
-      <c r="E5" s="13">
+      <c r="E5" s="19">
         <f>D5*(1+Assumptions!B$26)</f>
         <v/>
       </c>
-      <c r="F5" s="13">
+      <c r="F5" s="19">
         <f>E5*(1+Assumptions!C$26)</f>
         <v/>
       </c>
-      <c r="G5" s="13">
+      <c r="G5" s="19">
         <f>F5*(1+Assumptions!D$26)</f>
         <v/>
       </c>
-      <c r="H5" s="13">
+      <c r="H5" s="19">
         <f>G5*(1+Assumptions!E$26)</f>
         <v/>
       </c>
-      <c r="I5" s="13">
+      <c r="I5" s="19">
         <f>H5*(1+Assumptions!F$26)</f>
+        <v/>
+      </c>
+      <c r="J5" s="19">
+        <f>I5*(1+Assumptions!G$26)</f>
+        <v/>
+      </c>
+      <c r="K5" s="19">
+        <f>J5*(1+Assumptions!H$26)</f>
+        <v/>
+      </c>
+      <c r="L5" s="19">
+        <f>K5*(1+Assumptions!I$26)</f>
+        <v/>
+      </c>
+      <c r="M5" s="19">
+        <f>L5*(1+Assumptions!J$26)</f>
+        <v/>
+      </c>
+      <c r="N5" s="19">
+        <f>M5*(1+Assumptions!K$26)</f>
         <v/>
       </c>
     </row>
@@ -4007,32 +3995,52 @@
           <t xml:space="preserve">  growth %</t>
         </is>
       </c>
-      <c r="C6" s="30">
+      <c r="C6" s="26">
         <f>C5/B5-1</f>
         <v/>
       </c>
-      <c r="D6" s="30">
+      <c r="D6" s="26">
         <f>D5/C5-1</f>
         <v/>
       </c>
-      <c r="E6" s="14">
+      <c r="E6" s="12">
         <f>E5/D5-1</f>
         <v/>
       </c>
-      <c r="F6" s="14">
+      <c r="F6" s="12">
         <f>F5/E5-1</f>
         <v/>
       </c>
-      <c r="G6" s="14">
+      <c r="G6" s="12">
         <f>G5/F5-1</f>
         <v/>
       </c>
-      <c r="H6" s="14">
+      <c r="H6" s="12">
         <f>H5/G5-1</f>
         <v/>
       </c>
-      <c r="I6" s="14">
+      <c r="I6" s="12">
         <f>I5/H5-1</f>
+        <v/>
+      </c>
+      <c r="J6" s="12">
+        <f>J5/I5-1</f>
+        <v/>
+      </c>
+      <c r="K6" s="12">
+        <f>K5/J5-1</f>
+        <v/>
+      </c>
+      <c r="L6" s="12">
+        <f>L5/K5-1</f>
+        <v/>
+      </c>
+      <c r="M6" s="12">
+        <f>M5/L5-1</f>
+        <v/>
+      </c>
+      <c r="N6" s="12">
+        <f>N5/M5-1</f>
         <v/>
       </c>
     </row>
@@ -4042,33 +4050,53 @@
           <t>EBIT</t>
         </is>
       </c>
-      <c r="B7" s="29" t="n">
+      <c r="B7" s="25" t="n">
         <v>-1295</v>
       </c>
-      <c r="C7" s="29" t="n">
+      <c r="C7" s="25" t="n">
         <v>-444</v>
       </c>
-      <c r="D7" s="29" t="n">
+      <c r="D7" s="25" t="n">
         <v>507</v>
       </c>
-      <c r="E7" s="13">
+      <c r="E7" s="19">
         <f>E5*Assumptions!B$27</f>
         <v/>
       </c>
-      <c r="F7" s="13">
+      <c r="F7" s="19">
         <f>F5*Assumptions!C$27</f>
         <v/>
       </c>
-      <c r="G7" s="13">
+      <c r="G7" s="19">
         <f>G5*Assumptions!D$27</f>
         <v/>
       </c>
-      <c r="H7" s="13">
+      <c r="H7" s="19">
         <f>H5*Assumptions!E$27</f>
         <v/>
       </c>
-      <c r="I7" s="13">
+      <c r="I7" s="19">
         <f>I5*Assumptions!F$27</f>
+        <v/>
+      </c>
+      <c r="J7" s="19">
+        <f>J5*Assumptions!G$27</f>
+        <v/>
+      </c>
+      <c r="K7" s="19">
+        <f>K5*Assumptions!H$27</f>
+        <v/>
+      </c>
+      <c r="L7" s="19">
+        <f>L5*Assumptions!I$27</f>
+        <v/>
+      </c>
+      <c r="M7" s="19">
+        <f>M5*Assumptions!J$27</f>
+        <v/>
+      </c>
+      <c r="N7" s="19">
+        <f>N5*Assumptions!K$27</f>
         <v/>
       </c>
     </row>
@@ -4078,36 +4106,56 @@
           <t xml:space="preserve">  EBIT margin %</t>
         </is>
       </c>
-      <c r="B8" s="30">
+      <c r="B8" s="26">
         <f>B7/B5</f>
         <v/>
       </c>
-      <c r="C8" s="30">
+      <c r="C8" s="26">
         <f>C7/C5</f>
         <v/>
       </c>
-      <c r="D8" s="30">
+      <c r="D8" s="26">
         <f>D7/D5</f>
         <v/>
       </c>
-      <c r="E8" s="14">
+      <c r="E8" s="12">
         <f>E7/E5</f>
         <v/>
       </c>
-      <c r="F8" s="14">
+      <c r="F8" s="12">
         <f>F7/F5</f>
         <v/>
       </c>
-      <c r="G8" s="14">
+      <c r="G8" s="12">
         <f>G7/G5</f>
         <v/>
       </c>
-      <c r="H8" s="14">
+      <c r="H8" s="12">
         <f>H7/H5</f>
         <v/>
       </c>
-      <c r="I8" s="14">
+      <c r="I8" s="12">
         <f>I7/I5</f>
+        <v/>
+      </c>
+      <c r="J8" s="12">
+        <f>J7/J5</f>
+        <v/>
+      </c>
+      <c r="K8" s="12">
+        <f>K7/K5</f>
+        <v/>
+      </c>
+      <c r="L8" s="12">
+        <f>L7/L5</f>
+        <v/>
+      </c>
+      <c r="M8" s="12">
+        <f>M7/M5</f>
+        <v/>
+      </c>
+      <c r="N8" s="12">
+        <f>N7/N5</f>
         <v/>
       </c>
     </row>
@@ -4117,33 +4165,53 @@
           <t>D&amp;A</t>
         </is>
       </c>
-      <c r="B9" s="29" t="n">
+      <c r="B9" s="25" t="n">
         <v>448</v>
       </c>
-      <c r="C9" s="29" t="n">
+      <c r="C9" s="25" t="n">
         <v>224</v>
       </c>
-      <c r="D9" s="29" t="n">
+      <c r="D9" s="25" t="n">
         <v>163</v>
       </c>
-      <c r="E9" s="13">
+      <c r="E9" s="19">
         <f>E5*Assumptions!B$28</f>
         <v/>
       </c>
-      <c r="F9" s="13">
+      <c r="F9" s="19">
         <f>F5*Assumptions!C$28</f>
         <v/>
       </c>
-      <c r="G9" s="13">
+      <c r="G9" s="19">
         <f>G5*Assumptions!D$28</f>
         <v/>
       </c>
-      <c r="H9" s="13">
+      <c r="H9" s="19">
         <f>H5*Assumptions!E$28</f>
         <v/>
       </c>
-      <c r="I9" s="13">
+      <c r="I9" s="19">
         <f>I5*Assumptions!F$28</f>
+        <v/>
+      </c>
+      <c r="J9" s="19">
+        <f>J5*Assumptions!G$28</f>
+        <v/>
+      </c>
+      <c r="K9" s="19">
+        <f>K5*Assumptions!H$28</f>
+        <v/>
+      </c>
+      <c r="L9" s="19">
+        <f>L5*Assumptions!I$28</f>
+        <v/>
+      </c>
+      <c r="M9" s="19">
+        <f>M5*Assumptions!J$28</f>
+        <v/>
+      </c>
+      <c r="N9" s="19">
+        <f>N5*Assumptions!K$28</f>
         <v/>
       </c>
     </row>
@@ -4153,36 +4221,56 @@
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="B10" s="31">
+      <c r="B10" s="27">
         <f>B7+B9</f>
         <v/>
       </c>
-      <c r="C10" s="31">
+      <c r="C10" s="27">
         <f>C7+C9</f>
         <v/>
       </c>
-      <c r="D10" s="31">
+      <c r="D10" s="27">
         <f>D7+D9</f>
         <v/>
       </c>
-      <c r="E10" s="13">
+      <c r="E10" s="19">
         <f>E7+E9</f>
         <v/>
       </c>
-      <c r="F10" s="13">
+      <c r="F10" s="19">
         <f>F7+F9</f>
         <v/>
       </c>
-      <c r="G10" s="13">
+      <c r="G10" s="19">
         <f>G7+G9</f>
         <v/>
       </c>
-      <c r="H10" s="13">
+      <c r="H10" s="19">
         <f>H7+H9</f>
         <v/>
       </c>
-      <c r="I10" s="13">
+      <c r="I10" s="19">
         <f>I7+I9</f>
+        <v/>
+      </c>
+      <c r="J10" s="19">
+        <f>J7+J9</f>
+        <v/>
+      </c>
+      <c r="K10" s="19">
+        <f>K7+K9</f>
+        <v/>
+      </c>
+      <c r="L10" s="19">
+        <f>L7+L9</f>
+        <v/>
+      </c>
+      <c r="M10" s="19">
+        <f>M7+M9</f>
+        <v/>
+      </c>
+      <c r="N10" s="19">
+        <f>N7+N9</f>
         <v/>
       </c>
     </row>
@@ -4192,36 +4280,56 @@
           <t>NOPAT (EBIT×(1−t))</t>
         </is>
       </c>
-      <c r="B11" s="32">
+      <c r="B11" s="28">
         <f>B7*(1-Assumptions!$B$19)</f>
         <v/>
       </c>
-      <c r="C11" s="32">
+      <c r="C11" s="28">
         <f>C7*(1-Assumptions!$B$19)</f>
         <v/>
       </c>
-      <c r="D11" s="32">
+      <c r="D11" s="28">
         <f>D7*(1-Assumptions!$B$19)</f>
         <v/>
       </c>
-      <c r="E11" s="27">
+      <c r="E11" s="23">
         <f>E7*(1-Assumptions!$B$19)</f>
         <v/>
       </c>
-      <c r="F11" s="27">
+      <c r="F11" s="23">
         <f>F7*(1-Assumptions!$B$19)</f>
         <v/>
       </c>
-      <c r="G11" s="27">
+      <c r="G11" s="23">
         <f>G7*(1-Assumptions!$B$19)</f>
         <v/>
       </c>
-      <c r="H11" s="27">
+      <c r="H11" s="23">
         <f>H7*(1-Assumptions!$B$19)</f>
         <v/>
       </c>
-      <c r="I11" s="27">
+      <c r="I11" s="23">
         <f>I7*(1-Assumptions!$B$19)</f>
+        <v/>
+      </c>
+      <c r="J11" s="23">
+        <f>J7*(1-Assumptions!$B$19)</f>
+        <v/>
+      </c>
+      <c r="K11" s="23">
+        <f>K7*(1-Assumptions!$B$19)</f>
+        <v/>
+      </c>
+      <c r="L11" s="23">
+        <f>L7*(1-Assumptions!$B$19)</f>
+        <v/>
+      </c>
+      <c r="M11" s="23">
+        <f>M7*(1-Assumptions!$B$19)</f>
+        <v/>
+      </c>
+      <c r="N11" s="23">
+        <f>N7*(1-Assumptions!$B$19)</f>
         <v/>
       </c>
     </row>
@@ -4231,33 +4339,53 @@
           <t>Capex</t>
         </is>
       </c>
-      <c r="B12" s="29" t="n">
+      <c r="B12" s="25" t="n">
         <v>219</v>
       </c>
-      <c r="C12" s="29" t="n">
+      <c r="C12" s="25" t="n">
         <v>166</v>
       </c>
-      <c r="D12" s="29" t="n">
+      <c r="D12" s="25" t="n">
         <v>204</v>
       </c>
-      <c r="E12" s="13">
+      <c r="E12" s="19">
         <f>E5*Assumptions!B$29</f>
         <v/>
       </c>
-      <c r="F12" s="13">
+      <c r="F12" s="19">
         <f>F5*Assumptions!C$29</f>
         <v/>
       </c>
-      <c r="G12" s="13">
+      <c r="G12" s="19">
         <f>G5*Assumptions!D$29</f>
         <v/>
       </c>
-      <c r="H12" s="13">
+      <c r="H12" s="19">
         <f>H5*Assumptions!E$29</f>
         <v/>
       </c>
-      <c r="I12" s="13">
+      <c r="I12" s="19">
         <f>I5*Assumptions!F$29</f>
+        <v/>
+      </c>
+      <c r="J12" s="19">
+        <f>J5*Assumptions!G$29</f>
+        <v/>
+      </c>
+      <c r="K12" s="19">
+        <f>K5*Assumptions!H$29</f>
+        <v/>
+      </c>
+      <c r="L12" s="19">
+        <f>L5*Assumptions!I$29</f>
+        <v/>
+      </c>
+      <c r="M12" s="19">
+        <f>M5*Assumptions!J$29</f>
+        <v/>
+      </c>
+      <c r="N12" s="19">
+        <f>N5*Assumptions!K$29</f>
         <v/>
       </c>
     </row>
@@ -4267,72 +4395,112 @@
           <t>Δ Net working capital</t>
         </is>
       </c>
-      <c r="B13" s="29" t="n">
+      <c r="B13" s="25" t="n">
         <v>-197</v>
       </c>
-      <c r="C13" s="29" t="n">
+      <c r="C13" s="25" t="n">
         <v>86</v>
       </c>
-      <c r="D13" s="29" t="n">
+      <c r="D13" s="25" t="n">
         <v>380</v>
       </c>
-      <c r="E13" s="13">
+      <c r="E13" s="19">
         <f>(E5-D5)*Assumptions!$B$30</f>
         <v/>
       </c>
-      <c r="F13" s="13">
+      <c r="F13" s="19">
         <f>(F5-E5)*Assumptions!$B$30</f>
         <v/>
       </c>
-      <c r="G13" s="13">
+      <c r="G13" s="19">
         <f>(G5-F5)*Assumptions!$B$30</f>
         <v/>
       </c>
-      <c r="H13" s="13">
+      <c r="H13" s="19">
         <f>(H5-G5)*Assumptions!$B$30</f>
         <v/>
       </c>
-      <c r="I13" s="13">
+      <c r="I13" s="19">
         <f>(I5-H5)*Assumptions!$B$30</f>
         <v/>
       </c>
+      <c r="J13" s="19">
+        <f>(J5-I5)*Assumptions!$B$30</f>
+        <v/>
+      </c>
+      <c r="K13" s="19">
+        <f>(K5-J5)*Assumptions!$B$30</f>
+        <v/>
+      </c>
+      <c r="L13" s="19">
+        <f>(L5-K5)*Assumptions!$B$30</f>
+        <v/>
+      </c>
+      <c r="M13" s="19">
+        <f>(M5-L5)*Assumptions!$B$30</f>
+        <v/>
+      </c>
+      <c r="N13" s="19">
+        <f>(N5-M5)*Assumptions!$B$30</f>
+        <v/>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="11" t="inlineStr">
+      <c r="A14" s="13" t="inlineStr">
         <is>
           <t>FCFF</t>
         </is>
       </c>
-      <c r="B14" s="33">
+      <c r="B14" s="29">
         <f>B11+B9-B12-B13</f>
         <v/>
       </c>
-      <c r="C14" s="33">
+      <c r="C14" s="29">
         <f>C11+C9-C12-C13</f>
         <v/>
       </c>
-      <c r="D14" s="33">
+      <c r="D14" s="29">
         <f>D11+D9-D12-D13</f>
         <v/>
       </c>
-      <c r="E14" s="23">
+      <c r="E14" s="30">
         <f>E11+E9-E12-E13</f>
         <v/>
       </c>
-      <c r="F14" s="23">
+      <c r="F14" s="30">
         <f>F11+F9-F12-F13</f>
         <v/>
       </c>
-      <c r="G14" s="23">
+      <c r="G14" s="30">
         <f>G11+G9-G12-G13</f>
         <v/>
       </c>
-      <c r="H14" s="23">
+      <c r="H14" s="30">
         <f>H11+H9-H12-H13</f>
         <v/>
       </c>
-      <c r="I14" s="23">
+      <c r="I14" s="30">
         <f>I11+I9-I12-I13</f>
+        <v/>
+      </c>
+      <c r="J14" s="30">
+        <f>J11+J9-J12-J13</f>
+        <v/>
+      </c>
+      <c r="K14" s="30">
+        <f>K11+K9-K12-K13</f>
+        <v/>
+      </c>
+      <c r="L14" s="30">
+        <f>L11+L9-L12-L13</f>
+        <v/>
+      </c>
+      <c r="M14" s="30">
+        <f>M11+M9-M12-M13</f>
+        <v/>
+      </c>
+      <c r="N14" s="30">
+        <f>N11+N9-N12-N13</f>
         <v/>
       </c>
     </row>
@@ -4347,7 +4515,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:K25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -4357,6 +4525,11 @@
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4404,6 +4577,31 @@
           <t>FY2030E</t>
         </is>
       </c>
+      <c r="G4" s="10" t="inlineStr">
+        <is>
+          <t>FY2031E</t>
+        </is>
+      </c>
+      <c r="H4" s="10" t="inlineStr">
+        <is>
+          <t>FY2032E</t>
+        </is>
+      </c>
+      <c r="I4" s="10" t="inlineStr">
+        <is>
+          <t>FY2033E</t>
+        </is>
+      </c>
+      <c r="J4" s="10" t="inlineStr">
+        <is>
+          <t>FY2034E</t>
+        </is>
+      </c>
+      <c r="K4" s="10" t="inlineStr">
+        <is>
+          <t>FY2035E</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -4411,24 +4609,44 @@
           <t>FCFF (from Model)</t>
         </is>
       </c>
-      <c r="B5" s="27">
+      <c r="B5" s="23">
         <f>Model!E14</f>
         <v/>
       </c>
-      <c r="C5" s="27">
+      <c r="C5" s="23">
         <f>Model!F14</f>
         <v/>
       </c>
-      <c r="D5" s="27">
+      <c r="D5" s="23">
         <f>Model!G14</f>
         <v/>
       </c>
-      <c r="E5" s="27">
+      <c r="E5" s="23">
         <f>Model!H14</f>
         <v/>
       </c>
-      <c r="F5" s="27">
+      <c r="F5" s="23">
         <f>Model!I14</f>
+        <v/>
+      </c>
+      <c r="G5" s="23">
+        <f>Model!J14</f>
+        <v/>
+      </c>
+      <c r="H5" s="23">
+        <f>Model!K14</f>
+        <v/>
+      </c>
+      <c r="I5" s="23">
+        <f>Model!L14</f>
+        <v/>
+      </c>
+      <c r="J5" s="23">
+        <f>Model!M14</f>
+        <v/>
+      </c>
+      <c r="K5" s="23">
+        <f>Model!N14</f>
         <v/>
       </c>
     </row>
@@ -4438,20 +4656,35 @@
           <t>Period (mid-year, t−0.5)</t>
         </is>
       </c>
-      <c r="B6" s="34" t="n">
+      <c r="B6" s="31" t="n">
         <v>0.5</v>
       </c>
-      <c r="C6" s="34" t="n">
+      <c r="C6" s="31" t="n">
         <v>1.5</v>
       </c>
-      <c r="D6" s="34" t="n">
+      <c r="D6" s="31" t="n">
         <v>2.5</v>
       </c>
-      <c r="E6" s="34" t="n">
+      <c r="E6" s="31" t="n">
         <v>3.5</v>
       </c>
-      <c r="F6" s="34" t="n">
+      <c r="F6" s="31" t="n">
         <v>4.5</v>
+      </c>
+      <c r="G6" s="31" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="H6" s="31" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="I6" s="31" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="J6" s="31" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="K6" s="31" t="n">
+        <v>9.5</v>
       </c>
     </row>
     <row r="7">
@@ -4460,24 +4693,44 @@
           <t>Discount factor</t>
         </is>
       </c>
-      <c r="B7" s="35">
+      <c r="B7" s="32">
         <f>1/(1+WACC!$B$10)^B6</f>
         <v/>
       </c>
-      <c r="C7" s="35">
+      <c r="C7" s="32">
         <f>1/(1+WACC!$B$10)^C6</f>
         <v/>
       </c>
-      <c r="D7" s="35">
+      <c r="D7" s="32">
         <f>1/(1+WACC!$B$10)^D6</f>
         <v/>
       </c>
-      <c r="E7" s="35">
+      <c r="E7" s="32">
         <f>1/(1+WACC!$B$10)^E6</f>
         <v/>
       </c>
-      <c r="F7" s="35">
+      <c r="F7" s="32">
         <f>1/(1+WACC!$B$10)^F6</f>
+        <v/>
+      </c>
+      <c r="G7" s="32">
+        <f>1/(1+WACC!$B$10)^G6</f>
+        <v/>
+      </c>
+      <c r="H7" s="32">
+        <f>1/(1+WACC!$B$10)^H6</f>
+        <v/>
+      </c>
+      <c r="I7" s="32">
+        <f>1/(1+WACC!$B$10)^I6</f>
+        <v/>
+      </c>
+      <c r="J7" s="32">
+        <f>1/(1+WACC!$B$10)^J6</f>
+        <v/>
+      </c>
+      <c r="K7" s="32">
+        <f>1/(1+WACC!$B$10)^K6</f>
         <v/>
       </c>
     </row>
@@ -4487,24 +4740,44 @@
           <t>PV of FCFF</t>
         </is>
       </c>
-      <c r="B8" s="13">
+      <c r="B8" s="19">
         <f>B5*B7</f>
         <v/>
       </c>
-      <c r="C8" s="13">
+      <c r="C8" s="19">
         <f>C5*C7</f>
         <v/>
       </c>
-      <c r="D8" s="13">
+      <c r="D8" s="19">
         <f>D5*D7</f>
         <v/>
       </c>
-      <c r="E8" s="13">
+      <c r="E8" s="19">
         <f>E5*E7</f>
         <v/>
       </c>
-      <c r="F8" s="13">
+      <c r="F8" s="19">
         <f>F5*F7</f>
+        <v/>
+      </c>
+      <c r="G8" s="19">
+        <f>G5*G7</f>
+        <v/>
+      </c>
+      <c r="H8" s="19">
+        <f>H5*H7</f>
+        <v/>
+      </c>
+      <c r="I8" s="19">
+        <f>I5*I7</f>
+        <v/>
+      </c>
+      <c r="J8" s="19">
+        <f>J5*J7</f>
+        <v/>
+      </c>
+      <c r="K8" s="19">
+        <f>K5*K7</f>
         <v/>
       </c>
     </row>
@@ -4514,8 +4787,8 @@
           <t>PV of explicit FCFF</t>
         </is>
       </c>
-      <c r="B10" s="13">
-        <f>SUM(B8:F8)</f>
+      <c r="B10" s="19">
+        <f>SUM(B8:K8)</f>
         <v/>
       </c>
     </row>
@@ -4525,8 +4798,8 @@
           <t>Terminal NOPAT (FYn)</t>
         </is>
       </c>
-      <c r="B11" s="27">
-        <f>Model!I11</f>
+      <c r="B11" s="23">
+        <f>Model!N11</f>
         <v/>
       </c>
     </row>
@@ -4536,7 +4809,7 @@
           <t>Invested capital (mm)</t>
         </is>
       </c>
-      <c r="B12" s="12" t="n">
+      <c r="B12" s="18" t="n">
         <v>9777</v>
       </c>
     </row>
@@ -4546,8 +4819,8 @@
           <t>Terminal invested capital (scaled w/ revenue)</t>
         </is>
       </c>
-      <c r="B13" s="27">
-        <f>$B$12*Model!I5/Model!D5</f>
+      <c r="B13" s="23">
+        <f>$B$12*Model!N5/Model!D5</f>
         <v/>
       </c>
     </row>
@@ -4557,7 +4830,7 @@
           <t>Terminal ROIC</t>
         </is>
       </c>
-      <c r="B14" s="14">
+      <c r="B14" s="12">
         <f>MAX($B$11/$B$13,WACC!$B$10)</f>
         <v/>
       </c>
@@ -4568,7 +4841,7 @@
           <t>Terminal reinvestment rate (g/ROIC)</t>
         </is>
       </c>
-      <c r="B15" s="36">
+      <c r="B15" s="33">
         <f>Assumptions!$B$22/$B$14</f>
         <v/>
       </c>
@@ -4579,7 +4852,7 @@
           <t>Terminal value (Gordon)</t>
         </is>
       </c>
-      <c r="B16" s="13">
+      <c r="B16" s="19">
         <f>$B$11*(1+Assumptions!$B$22)*(1-$B$15)/(WACC!$B$10-Assumptions!$B$22)</f>
         <v/>
       </c>
@@ -4590,8 +4863,8 @@
           <t>PV of terminal value</t>
         </is>
       </c>
-      <c r="B17" s="13">
-        <f>$B$16/(1+WACC!$B$10)^(5-0.5)</f>
+      <c r="B17" s="19">
+        <f>$B$16/(1+WACC!$B$10)^(10-0.5)</f>
         <v/>
       </c>
     </row>
@@ -4601,18 +4874,18 @@
           <t>TV as % of EV</t>
         </is>
       </c>
-      <c r="B18" s="14">
+      <c r="B18" s="12">
         <f>$B$17/($B$10+$B$17)</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="11" t="inlineStr">
+      <c r="A20" s="13" t="inlineStr">
         <is>
           <t>Enterprise value</t>
         </is>
       </c>
-      <c r="B20" s="23">
+      <c r="B20" s="30">
         <f>$B$10+$B$17</f>
         <v/>
       </c>
@@ -4623,7 +4896,7 @@
           <t>(−) Net debt</t>
         </is>
       </c>
-      <c r="B21" s="27">
+      <c r="B21" s="23">
         <f>-Assumptions!$B$10</f>
         <v/>
       </c>
@@ -4634,40 +4907,40 @@
           <t>(−) Minority interest</t>
         </is>
       </c>
-      <c r="B22" s="27">
+      <c r="B22" s="23">
         <f>-Assumptions!$B$9</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="11" t="inlineStr">
+      <c r="A23" s="13" t="inlineStr">
         <is>
           <t>Equity value</t>
         </is>
       </c>
-      <c r="B23" s="23">
+      <c r="B23" s="30">
         <f>$B$20-Assumptions!$B$10-Assumptions!$B$9</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="11" t="inlineStr">
+      <c r="A24" s="13" t="inlineStr">
         <is>
           <t>Value per share</t>
         </is>
       </c>
-      <c r="B24" s="37">
+      <c r="B24" s="34">
         <f>$B$23/Assumptions!$B$6</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="11" t="inlineStr">
+      <c r="A25" s="13" t="inlineStr">
         <is>
           <t>Upside vs price</t>
         </is>
       </c>
-      <c r="B25" s="38">
+      <c r="B25" s="35">
         <f>$B$24/Assumptions!$B$5-1</f>
         <v/>
       </c>
@@ -4709,149 +4982,149 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="11" t="inlineStr">
+      <c r="A4" s="13" t="inlineStr">
         <is>
           <t>WACC \ g</t>
         </is>
       </c>
-      <c r="B4" s="15" t="n">
+      <c r="B4" s="11" t="n">
         <v>0.015</v>
       </c>
-      <c r="C4" s="15" t="n">
+      <c r="C4" s="11" t="n">
         <v>0.02</v>
       </c>
-      <c r="D4" s="15" t="n">
+      <c r="D4" s="11" t="n">
         <v>0.025</v>
       </c>
-      <c r="E4" s="15" t="n">
+      <c r="E4" s="11" t="n">
         <v>0.03</v>
       </c>
-      <c r="F4" s="15" t="n">
+      <c r="F4" s="11" t="n">
         <v>0.035</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="18" t="n">
-        <v>0.07359804659680111</v>
+      <c r="A5" s="15" t="n">
+        <v>0.07846218739538</v>
       </c>
       <c r="B5" s="16">
-        <f>(SUMPRODUCT(DCF!$B$5:$F$5,1/(1+$A$5)^DCF!$B$6:$F$6)+DCF!$B$11*(1+B$4)*(1-B$4/DCF!$B$14)/($A$5-B$4)/(1+$A$5)^(5-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$5:$K$5,1/(1+$A$5)^DCF!$B$6:$K$6)+DCF!$B$11*(1+B$4)*(1-B$4/DCF!$B$14)/($A$5-B$4)/(1+$A$5)^(10-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
         <v/>
       </c>
       <c r="C5" s="16">
-        <f>(SUMPRODUCT(DCF!$B$5:$F$5,1/(1+$A$5)^DCF!$B$6:$F$6)+DCF!$B$11*(1+C$4)*(1-C$4/DCF!$B$14)/($A$5-C$4)/(1+$A$5)^(5-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$5:$K$5,1/(1+$A$5)^DCF!$B$6:$K$6)+DCF!$B$11*(1+C$4)*(1-C$4/DCF!$B$14)/($A$5-C$4)/(1+$A$5)^(10-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
         <v/>
       </c>
       <c r="D5" s="16">
-        <f>(SUMPRODUCT(DCF!$B$5:$F$5,1/(1+$A$5)^DCF!$B$6:$F$6)+DCF!$B$11*(1+D$4)*(1-D$4/DCF!$B$14)/($A$5-D$4)/(1+$A$5)^(5-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$5:$K$5,1/(1+$A$5)^DCF!$B$6:$K$6)+DCF!$B$11*(1+D$4)*(1-D$4/DCF!$B$14)/($A$5-D$4)/(1+$A$5)^(10-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
         <v/>
       </c>
       <c r="E5" s="16">
-        <f>(SUMPRODUCT(DCF!$B$5:$F$5,1/(1+$A$5)^DCF!$B$6:$F$6)+DCF!$B$11*(1+E$4)*(1-E$4/DCF!$B$14)/($A$5-E$4)/(1+$A$5)^(5-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$5:$K$5,1/(1+$A$5)^DCF!$B$6:$K$6)+DCF!$B$11*(1+E$4)*(1-E$4/DCF!$B$14)/($A$5-E$4)/(1+$A$5)^(10-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
         <v/>
       </c>
       <c r="F5" s="16">
-        <f>(SUMPRODUCT(DCF!$B$5:$F$5,1/(1+$A$5)^DCF!$B$6:$F$6)+DCF!$B$11*(1+F$4)*(1-F$4/DCF!$B$14)/($A$5-F$4)/(1+$A$5)^(5-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$5:$K$5,1/(1+$A$5)^DCF!$B$6:$K$6)+DCF!$B$11*(1+F$4)*(1-F$4/DCF!$B$14)/($A$5-F$4)/(1+$A$5)^(10-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="18" t="n">
-        <v>0.08109804659680112</v>
+      <c r="A6" s="15" t="n">
+        <v>0.08596218739538</v>
       </c>
       <c r="B6" s="16">
-        <f>(SUMPRODUCT(DCF!$B$5:$F$5,1/(1+$A$6)^DCF!$B$6:$F$6)+DCF!$B$11*(1+B$4)*(1-B$4/DCF!$B$14)/($A$6-B$4)/(1+$A$6)^(5-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$5:$K$5,1/(1+$A$6)^DCF!$B$6:$K$6)+DCF!$B$11*(1+B$4)*(1-B$4/DCF!$B$14)/($A$6-B$4)/(1+$A$6)^(10-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
         <v/>
       </c>
       <c r="C6" s="16">
-        <f>(SUMPRODUCT(DCF!$B$5:$F$5,1/(1+$A$6)^DCF!$B$6:$F$6)+DCF!$B$11*(1+C$4)*(1-C$4/DCF!$B$14)/($A$6-C$4)/(1+$A$6)^(5-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$5:$K$5,1/(1+$A$6)^DCF!$B$6:$K$6)+DCF!$B$11*(1+C$4)*(1-C$4/DCF!$B$14)/($A$6-C$4)/(1+$A$6)^(10-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
         <v/>
       </c>
       <c r="D6" s="16">
-        <f>(SUMPRODUCT(DCF!$B$5:$F$5,1/(1+$A$6)^DCF!$B$6:$F$6)+DCF!$B$11*(1+D$4)*(1-D$4/DCF!$B$14)/($A$6-D$4)/(1+$A$6)^(5-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$5:$K$5,1/(1+$A$6)^DCF!$B$6:$K$6)+DCF!$B$11*(1+D$4)*(1-D$4/DCF!$B$14)/($A$6-D$4)/(1+$A$6)^(10-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
         <v/>
       </c>
       <c r="E6" s="16">
-        <f>(SUMPRODUCT(DCF!$B$5:$F$5,1/(1+$A$6)^DCF!$B$6:$F$6)+DCF!$B$11*(1+E$4)*(1-E$4/DCF!$B$14)/($A$6-E$4)/(1+$A$6)^(5-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$5:$K$5,1/(1+$A$6)^DCF!$B$6:$K$6)+DCF!$B$11*(1+E$4)*(1-E$4/DCF!$B$14)/($A$6-E$4)/(1+$A$6)^(10-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
         <v/>
       </c>
       <c r="F6" s="16">
-        <f>(SUMPRODUCT(DCF!$B$5:$F$5,1/(1+$A$6)^DCF!$B$6:$F$6)+DCF!$B$11*(1+F$4)*(1-F$4/DCF!$B$14)/($A$6-F$4)/(1+$A$6)^(5-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$5:$K$5,1/(1+$A$6)^DCF!$B$6:$K$6)+DCF!$B$11*(1+F$4)*(1-F$4/DCF!$B$14)/($A$6-F$4)/(1+$A$6)^(10-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="18" t="n">
-        <v>0.08859804659680111</v>
+      <c r="A7" s="15" t="n">
+        <v>0.09346218739537999</v>
       </c>
       <c r="B7" s="16">
-        <f>(SUMPRODUCT(DCF!$B$5:$F$5,1/(1+$A$7)^DCF!$B$6:$F$6)+DCF!$B$11*(1+B$4)*(1-B$4/DCF!$B$14)/($A$7-B$4)/(1+$A$7)^(5-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$5:$K$5,1/(1+$A$7)^DCF!$B$6:$K$6)+DCF!$B$11*(1+B$4)*(1-B$4/DCF!$B$14)/($A$7-B$4)/(1+$A$7)^(10-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
         <v/>
       </c>
       <c r="C7" s="16">
-        <f>(SUMPRODUCT(DCF!$B$5:$F$5,1/(1+$A$7)^DCF!$B$6:$F$6)+DCF!$B$11*(1+C$4)*(1-C$4/DCF!$B$14)/($A$7-C$4)/(1+$A$7)^(5-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$5:$K$5,1/(1+$A$7)^DCF!$B$6:$K$6)+DCF!$B$11*(1+C$4)*(1-C$4/DCF!$B$14)/($A$7-C$4)/(1+$A$7)^(10-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
         <v/>
       </c>
       <c r="D7" s="16">
-        <f>(SUMPRODUCT(DCF!$B$5:$F$5,1/(1+$A$7)^DCF!$B$6:$F$6)+DCF!$B$11*(1+D$4)*(1-D$4/DCF!$B$14)/($A$7-D$4)/(1+$A$7)^(5-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$5:$K$5,1/(1+$A$7)^DCF!$B$6:$K$6)+DCF!$B$11*(1+D$4)*(1-D$4/DCF!$B$14)/($A$7-D$4)/(1+$A$7)^(10-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
         <v/>
       </c>
       <c r="E7" s="16">
-        <f>(SUMPRODUCT(DCF!$B$5:$F$5,1/(1+$A$7)^DCF!$B$6:$F$6)+DCF!$B$11*(1+E$4)*(1-E$4/DCF!$B$14)/($A$7-E$4)/(1+$A$7)^(5-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$5:$K$5,1/(1+$A$7)^DCF!$B$6:$K$6)+DCF!$B$11*(1+E$4)*(1-E$4/DCF!$B$14)/($A$7-E$4)/(1+$A$7)^(10-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
         <v/>
       </c>
       <c r="F7" s="16">
-        <f>(SUMPRODUCT(DCF!$B$5:$F$5,1/(1+$A$7)^DCF!$B$6:$F$6)+DCF!$B$11*(1+F$4)*(1-F$4/DCF!$B$14)/($A$7-F$4)/(1+$A$7)^(5-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$5:$K$5,1/(1+$A$7)^DCF!$B$6:$K$6)+DCF!$B$11*(1+F$4)*(1-F$4/DCF!$B$14)/($A$7-F$4)/(1+$A$7)^(10-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="18" t="n">
-        <v>0.0960980465968011</v>
+      <c r="A8" s="15" t="n">
+        <v>0.10096218739538</v>
       </c>
       <c r="B8" s="16">
-        <f>(SUMPRODUCT(DCF!$B$5:$F$5,1/(1+$A$8)^DCF!$B$6:$F$6)+DCF!$B$11*(1+B$4)*(1-B$4/DCF!$B$14)/($A$8-B$4)/(1+$A$8)^(5-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$5:$K$5,1/(1+$A$8)^DCF!$B$6:$K$6)+DCF!$B$11*(1+B$4)*(1-B$4/DCF!$B$14)/($A$8-B$4)/(1+$A$8)^(10-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
         <v/>
       </c>
       <c r="C8" s="16">
-        <f>(SUMPRODUCT(DCF!$B$5:$F$5,1/(1+$A$8)^DCF!$B$6:$F$6)+DCF!$B$11*(1+C$4)*(1-C$4/DCF!$B$14)/($A$8-C$4)/(1+$A$8)^(5-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$5:$K$5,1/(1+$A$8)^DCF!$B$6:$K$6)+DCF!$B$11*(1+C$4)*(1-C$4/DCF!$B$14)/($A$8-C$4)/(1+$A$8)^(10-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
         <v/>
       </c>
       <c r="D8" s="16">
-        <f>(SUMPRODUCT(DCF!$B$5:$F$5,1/(1+$A$8)^DCF!$B$6:$F$6)+DCF!$B$11*(1+D$4)*(1-D$4/DCF!$B$14)/($A$8-D$4)/(1+$A$8)^(5-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$5:$K$5,1/(1+$A$8)^DCF!$B$6:$K$6)+DCF!$B$11*(1+D$4)*(1-D$4/DCF!$B$14)/($A$8-D$4)/(1+$A$8)^(10-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
         <v/>
       </c>
       <c r="E8" s="16">
-        <f>(SUMPRODUCT(DCF!$B$5:$F$5,1/(1+$A$8)^DCF!$B$6:$F$6)+DCF!$B$11*(1+E$4)*(1-E$4/DCF!$B$14)/($A$8-E$4)/(1+$A$8)^(5-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$5:$K$5,1/(1+$A$8)^DCF!$B$6:$K$6)+DCF!$B$11*(1+E$4)*(1-E$4/DCF!$B$14)/($A$8-E$4)/(1+$A$8)^(10-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
         <v/>
       </c>
       <c r="F8" s="16">
-        <f>(SUMPRODUCT(DCF!$B$5:$F$5,1/(1+$A$8)^DCF!$B$6:$F$6)+DCF!$B$11*(1+F$4)*(1-F$4/DCF!$B$14)/($A$8-F$4)/(1+$A$8)^(5-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$5:$K$5,1/(1+$A$8)^DCF!$B$6:$K$6)+DCF!$B$11*(1+F$4)*(1-F$4/DCF!$B$14)/($A$8-F$4)/(1+$A$8)^(10-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="18" t="n">
-        <v>0.1035980465968011</v>
+      <c r="A9" s="15" t="n">
+        <v>0.10846218739538</v>
       </c>
       <c r="B9" s="16">
-        <f>(SUMPRODUCT(DCF!$B$5:$F$5,1/(1+$A$9)^DCF!$B$6:$F$6)+DCF!$B$11*(1+B$4)*(1-B$4/DCF!$B$14)/($A$9-B$4)/(1+$A$9)^(5-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$5:$K$5,1/(1+$A$9)^DCF!$B$6:$K$6)+DCF!$B$11*(1+B$4)*(1-B$4/DCF!$B$14)/($A$9-B$4)/(1+$A$9)^(10-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
         <v/>
       </c>
       <c r="C9" s="16">
-        <f>(SUMPRODUCT(DCF!$B$5:$F$5,1/(1+$A$9)^DCF!$B$6:$F$6)+DCF!$B$11*(1+C$4)*(1-C$4/DCF!$B$14)/($A$9-C$4)/(1+$A$9)^(5-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$5:$K$5,1/(1+$A$9)^DCF!$B$6:$K$6)+DCF!$B$11*(1+C$4)*(1-C$4/DCF!$B$14)/($A$9-C$4)/(1+$A$9)^(10-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
         <v/>
       </c>
       <c r="D9" s="16">
-        <f>(SUMPRODUCT(DCF!$B$5:$F$5,1/(1+$A$9)^DCF!$B$6:$F$6)+DCF!$B$11*(1+D$4)*(1-D$4/DCF!$B$14)/($A$9-D$4)/(1+$A$9)^(5-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$5:$K$5,1/(1+$A$9)^DCF!$B$6:$K$6)+DCF!$B$11*(1+D$4)*(1-D$4/DCF!$B$14)/($A$9-D$4)/(1+$A$9)^(10-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
         <v/>
       </c>
       <c r="E9" s="16">
-        <f>(SUMPRODUCT(DCF!$B$5:$F$5,1/(1+$A$9)^DCF!$B$6:$F$6)+DCF!$B$11*(1+E$4)*(1-E$4/DCF!$B$14)/($A$9-E$4)/(1+$A$9)^(5-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$5:$K$5,1/(1+$A$9)^DCF!$B$6:$K$6)+DCF!$B$11*(1+E$4)*(1-E$4/DCF!$B$14)/($A$9-E$4)/(1+$A$9)^(10-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
         <v/>
       </c>
       <c r="F9" s="16">
-        <f>(SUMPRODUCT(DCF!$B$5:$F$5,1/(1+$A$9)^DCF!$B$6:$F$6)+DCF!$B$11*(1+F$4)*(1-F$4/DCF!$B$14)/($A$9-F$4)/(1+$A$9)^(5-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$5:$K$5,1/(1+$A$9)^DCF!$B$6:$K$6)+DCF!$B$11*(1+F$4)*(1-F$4/DCF!$B$14)/($A$9-F$4)/(1+$A$9)^(10-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
         <v/>
       </c>
     </row>
@@ -4885,7 +5158,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>As reported by yfinance (USDmm). Hardcoded actuals.</t>
+          <t>As reported by Yahoo snapshot as of 2026-07-09 (USDmm). Hardcoded actuals.</t>
         </is>
       </c>
     </row>
@@ -4917,13 +5190,13 @@
           <t>Tax Effect Of Unusual Items</t>
         </is>
       </c>
-      <c r="B5" s="29" t="n">
+      <c r="B5" s="25" t="n">
         <v>-155.4</v>
       </c>
-      <c r="C5" s="29" t="n">
+      <c r="C5" s="25" t="n">
         <v>-5.04</v>
       </c>
-      <c r="D5" s="29" t="n">
+      <c r="D5" s="25" t="n">
         <v>-395.64</v>
       </c>
     </row>
@@ -4933,14 +5206,14 @@
           <t>Tax Rate For Calcs</t>
         </is>
       </c>
-      <c r="B6" s="29" t="n">
-        <v>2.1e-07</v>
-      </c>
-      <c r="C6" s="29" t="n">
-        <v>2.1e-07</v>
-      </c>
-      <c r="D6" s="29" t="n">
-        <v>2.1e-07</v>
+      <c r="B6" s="25" t="n">
+        <v>2.1e-13</v>
+      </c>
+      <c r="C6" s="25" t="n">
+        <v>2.1e-13</v>
+      </c>
+      <c r="D6" s="25" t="n">
+        <v>2.1e-13</v>
       </c>
     </row>
     <row r="7">
@@ -4949,13 +5222,13 @@
           <t>Normalized EBITDA</t>
         </is>
       </c>
-      <c r="B7" s="29" t="n">
+      <c r="B7" s="25" t="n">
         <v>-783</v>
       </c>
-      <c r="C7" s="29" t="n">
+      <c r="C7" s="25" t="n">
         <v>-215</v>
       </c>
-      <c r="D7" s="29" t="n">
+      <c r="D7" s="25" t="n">
         <v>631</v>
       </c>
     </row>
@@ -4965,13 +5238,13 @@
           <t>Total Unusual Items</t>
         </is>
       </c>
-      <c r="B8" s="29" t="n">
+      <c r="B8" s="25" t="n">
         <v>-740</v>
       </c>
-      <c r="C8" s="29" t="n">
+      <c r="C8" s="25" t="n">
         <v>-24</v>
       </c>
-      <c r="D8" s="29" t="n">
+      <c r="D8" s="25" t="n">
         <v>-1884</v>
       </c>
     </row>
@@ -4981,13 +5254,13 @@
           <t>Total Unusual Items Excluding Goodwill</t>
         </is>
       </c>
-      <c r="B9" s="29" t="n">
+      <c r="B9" s="25" t="n">
         <v>-740</v>
       </c>
-      <c r="C9" s="29" t="n">
+      <c r="C9" s="25" t="n">
         <v>-24</v>
       </c>
-      <c r="D9" s="29" t="n">
+      <c r="D9" s="25" t="n">
         <v>-1884</v>
       </c>
     </row>
@@ -4997,13 +5270,13 @@
           <t>Net Income From Continuing Operation Net Minority Interest</t>
         </is>
       </c>
-      <c r="B10" s="29" t="n">
+      <c r="B10" s="25" t="n">
         <v>-2143</v>
       </c>
-      <c r="C10" s="29" t="n">
+      <c r="C10" s="25" t="n">
         <v>-672</v>
       </c>
-      <c r="D10" s="29" t="n">
+      <c r="D10" s="25" t="n">
         <v>-1641</v>
       </c>
     </row>
@@ -5013,13 +5286,13 @@
           <t>Reconciled Depreciation</t>
         </is>
       </c>
-      <c r="B11" s="29" t="n">
+      <c r="B11" s="25" t="n">
         <v>448</v>
       </c>
-      <c r="C11" s="29" t="n">
+      <c r="C11" s="25" t="n">
         <v>224</v>
       </c>
-      <c r="D11" s="29" t="n">
+      <c r="D11" s="25" t="n">
         <v>163</v>
       </c>
     </row>
@@ -5029,13 +5302,13 @@
           <t>Reconciled Cost Of Revenue</t>
         </is>
       </c>
-      <c r="B12" s="29" t="n">
+      <c r="B12" s="25" t="n">
         <v>5656</v>
       </c>
-      <c r="C12" s="29" t="n">
+      <c r="C12" s="25" t="n">
         <v>5591</v>
       </c>
-      <c r="D12" s="29" t="n">
+      <c r="D12" s="25" t="n">
         <v>5143</v>
       </c>
     </row>
@@ -5045,13 +5318,13 @@
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="B13" s="29" t="n">
+      <c r="B13" s="25" t="n">
         <v>-1523</v>
       </c>
-      <c r="C13" s="29" t="n">
+      <c r="C13" s="25" t="n">
         <v>-239</v>
       </c>
-      <c r="D13" s="29" t="n">
+      <c r="D13" s="25" t="n">
         <v>-1253</v>
       </c>
     </row>
@@ -5061,13 +5334,13 @@
           <t>EBIT</t>
         </is>
       </c>
-      <c r="B14" s="29" t="n">
+      <c r="B14" s="25" t="n">
         <v>-1971</v>
       </c>
-      <c r="C14" s="29" t="n">
+      <c r="C14" s="25" t="n">
         <v>-463</v>
       </c>
-      <c r="D14" s="29" t="n">
+      <c r="D14" s="25" t="n">
         <v>-1416</v>
       </c>
     </row>
@@ -5077,13 +5350,13 @@
           <t>Net Interest Income</t>
         </is>
       </c>
-      <c r="B15" s="29" t="n">
+      <c r="B15" s="25" t="n">
         <v>-10</v>
       </c>
-      <c r="C15" s="29" t="n">
+      <c r="C15" s="25" t="n">
         <v>-28</v>
       </c>
-      <c r="D15" s="29" t="n">
+      <c r="D15" s="25" t="n">
         <v>-41</v>
       </c>
     </row>
@@ -5093,13 +5366,13 @@
           <t>Interest Expense</t>
         </is>
       </c>
-      <c r="B16" s="29" t="n">
+      <c r="B16" s="25" t="n">
         <v>31</v>
       </c>
-      <c r="C16" s="29" t="n">
+      <c r="C16" s="25" t="n">
         <v>40</v>
       </c>
-      <c r="D16" s="29" t="n">
+      <c r="D16" s="25" t="n">
         <v>63</v>
       </c>
     </row>
@@ -5109,13 +5382,13 @@
           <t>Interest Income</t>
         </is>
       </c>
-      <c r="B17" s="29" t="n">
+      <c r="B17" s="25" t="n">
         <v>21</v>
       </c>
-      <c r="C17" s="29" t="n">
+      <c r="C17" s="25" t="n">
         <v>12</v>
       </c>
-      <c r="D17" s="29" t="n">
+      <c r="D17" s="25" t="n">
         <v>22</v>
       </c>
     </row>
@@ -5125,13 +5398,13 @@
           <t>Normalized Income</t>
         </is>
       </c>
-      <c r="B18" s="29" t="n">
+      <c r="B18" s="25" t="n">
         <v>-1558.4</v>
       </c>
-      <c r="C18" s="29" t="n">
+      <c r="C18" s="25" t="n">
         <v>-653.04</v>
       </c>
-      <c r="D18" s="29" t="n">
+      <c r="D18" s="25" t="n">
         <v>-152.64</v>
       </c>
     </row>
@@ -5141,13 +5414,13 @@
           <t>Net Income From Continuing And Discontinued Operation</t>
         </is>
       </c>
-      <c r="B19" s="29" t="n">
+      <c r="B19" s="25" t="n">
         <v>-2143</v>
       </c>
-      <c r="C19" s="29" t="n">
+      <c r="C19" s="25" t="n">
         <v>-672</v>
       </c>
-      <c r="D19" s="29" t="n">
+      <c r="D19" s="25" t="n">
         <v>-1641</v>
       </c>
     </row>
@@ -5157,13 +5430,13 @@
           <t>Total Expenses</t>
         </is>
       </c>
-      <c r="B20" s="29" t="n">
+      <c r="B20" s="25" t="n">
         <v>7381</v>
       </c>
-      <c r="C20" s="29" t="n">
+      <c r="C20" s="25" t="n">
         <v>7107</v>
       </c>
-      <c r="D20" s="29" t="n">
+      <c r="D20" s="25" t="n">
         <v>6848</v>
       </c>
     </row>
@@ -5173,13 +5446,13 @@
           <t>Total Operating Income As Reported</t>
         </is>
       </c>
-      <c r="B21" s="29" t="n">
+      <c r="B21" s="25" t="n">
         <v>-2035</v>
       </c>
-      <c r="C21" s="29" t="n">
+      <c r="C21" s="25" t="n">
         <v>-468</v>
       </c>
-      <c r="D21" s="29" t="n">
+      <c r="D21" s="25" t="n">
         <v>-1377</v>
       </c>
     </row>
@@ -5189,13 +5462,13 @@
           <t>Diluted Average Shares</t>
         </is>
       </c>
-      <c r="B22" s="29" t="n">
+      <c r="B22" s="25" t="n">
         <v>145</v>
       </c>
-      <c r="C22" s="29" t="n">
+      <c r="C22" s="25" t="n">
         <v>145</v>
       </c>
-      <c r="D22" s="29" t="n">
+      <c r="D22" s="25" t="n">
         <v>145</v>
       </c>
     </row>
@@ -5205,13 +5478,13 @@
           <t>Basic Average Shares</t>
         </is>
       </c>
-      <c r="B23" s="29" t="n">
+      <c r="B23" s="25" t="n">
         <v>145</v>
       </c>
-      <c r="C23" s="29" t="n">
+      <c r="C23" s="25" t="n">
         <v>145</v>
       </c>
-      <c r="D23" s="29" t="n">
+      <c r="D23" s="25" t="n">
         <v>145</v>
       </c>
     </row>
@@ -5221,14 +5494,14 @@
           <t>Diluted EPS</t>
         </is>
       </c>
-      <c r="B24" s="29" t="n">
-        <v>-1.478e-05</v>
-      </c>
-      <c r="C24" s="29" t="n">
-        <v>-4.63e-06</v>
-      </c>
-      <c r="D24" s="29" t="n">
-        <v>-1.132e-05</v>
+      <c r="B24" s="25" t="n">
+        <v>-1.478e-11</v>
+      </c>
+      <c r="C24" s="25" t="n">
+        <v>-4.629999999999999e-12</v>
+      </c>
+      <c r="D24" s="25" t="n">
+        <v>-1.132e-11</v>
       </c>
     </row>
     <row r="25">
@@ -5237,14 +5510,14 @@
           <t>Basic EPS</t>
         </is>
       </c>
-      <c r="B25" s="29" t="n">
-        <v>-1.478e-05</v>
-      </c>
-      <c r="C25" s="29" t="n">
-        <v>-4.63e-06</v>
-      </c>
-      <c r="D25" s="29" t="n">
-        <v>-1.132e-05</v>
+      <c r="B25" s="25" t="n">
+        <v>-1.478e-11</v>
+      </c>
+      <c r="C25" s="25" t="n">
+        <v>-4.629999999999999e-12</v>
+      </c>
+      <c r="D25" s="25" t="n">
+        <v>-1.132e-11</v>
       </c>
     </row>
     <row r="26">
@@ -5253,13 +5526,13 @@
           <t>Diluted NI Availto Com Stockholders</t>
         </is>
       </c>
-      <c r="B26" s="29" t="n">
+      <c r="B26" s="25" t="n">
         <v>-2143</v>
       </c>
-      <c r="C26" s="29" t="n">
+      <c r="C26" s="25" t="n">
         <v>-672</v>
       </c>
-      <c r="D26" s="29" t="n">
+      <c r="D26" s="25" t="n">
         <v>-1641</v>
       </c>
     </row>
@@ -5269,13 +5542,13 @@
           <t>Net Income Common Stockholders</t>
         </is>
       </c>
-      <c r="B27" s="29" t="n">
+      <c r="B27" s="25" t="n">
         <v>-2143</v>
       </c>
-      <c r="C27" s="29" t="n">
+      <c r="C27" s="25" t="n">
         <v>-672</v>
       </c>
-      <c r="D27" s="29" t="n">
+      <c r="D27" s="25" t="n">
         <v>-1641</v>
       </c>
     </row>
@@ -5285,13 +5558,13 @@
           <t>Net Income</t>
         </is>
       </c>
-      <c r="B28" s="29" t="n">
+      <c r="B28" s="25" t="n">
         <v>-2143</v>
       </c>
-      <c r="C28" s="29" t="n">
+      <c r="C28" s="25" t="n">
         <v>-672</v>
       </c>
-      <c r="D28" s="29" t="n">
+      <c r="D28" s="25" t="n">
         <v>-1641</v>
       </c>
     </row>
@@ -5301,13 +5574,13 @@
           <t>Net Income Including Noncontrolling Interests</t>
         </is>
       </c>
-      <c r="B29" s="29" t="n">
+      <c r="B29" s="25" t="n">
         <v>-2143</v>
       </c>
-      <c r="C29" s="29" t="n">
+      <c r="C29" s="25" t="n">
         <v>-672</v>
       </c>
-      <c r="D29" s="29" t="n">
+      <c r="D29" s="25" t="n">
         <v>-1641</v>
       </c>
     </row>
@@ -5317,13 +5590,13 @@
           <t>Net Income Continuous Operations</t>
         </is>
       </c>
-      <c r="B30" s="29" t="n">
+      <c r="B30" s="25" t="n">
         <v>-2143</v>
       </c>
-      <c r="C30" s="29" t="n">
+      <c r="C30" s="25" t="n">
         <v>-672</v>
       </c>
-      <c r="D30" s="29" t="n">
+      <c r="D30" s="25" t="n">
         <v>-1641</v>
       </c>
     </row>
@@ -5333,13 +5606,13 @@
           <t>Tax Provision</t>
         </is>
       </c>
-      <c r="B31" s="29" t="n">
+      <c r="B31" s="25" t="n">
         <v>141</v>
       </c>
-      <c r="C31" s="29" t="n">
+      <c r="C31" s="25" t="n">
         <v>169</v>
       </c>
-      <c r="D31" s="29" t="n">
+      <c r="D31" s="25" t="n">
         <v>162</v>
       </c>
     </row>
@@ -5349,13 +5622,13 @@
           <t>Pretax Income</t>
         </is>
       </c>
-      <c r="B32" s="29" t="n">
+      <c r="B32" s="25" t="n">
         <v>-2002</v>
       </c>
-      <c r="C32" s="29" t="n">
+      <c r="C32" s="25" t="n">
         <v>-503</v>
       </c>
-      <c r="D32" s="29" t="n">
+      <c r="D32" s="25" t="n">
         <v>-1479</v>
       </c>
     </row>
@@ -5365,13 +5638,13 @@
           <t>Other Income Expense</t>
         </is>
       </c>
-      <c r="B33" s="29" t="n">
+      <c r="B33" s="25" t="n">
         <v>-697</v>
       </c>
-      <c r="C33" s="29" t="n">
+      <c r="C33" s="25" t="n">
         <v>-31</v>
       </c>
-      <c r="D33" s="29" t="n">
+      <c r="D33" s="25" t="n">
         <v>-1945</v>
       </c>
     </row>
@@ -5381,13 +5654,13 @@
           <t>Other Non Operating Income Expenses</t>
         </is>
       </c>
-      <c r="B34" s="29" t="n">
+      <c r="B34" s="25" t="n">
         <v>43</v>
       </c>
-      <c r="C34" s="29" t="n">
+      <c r="C34" s="25" t="n">
         <v>-7</v>
       </c>
-      <c r="D34" s="29" t="n">
+      <c r="D34" s="25" t="n">
         <v>-61</v>
       </c>
     </row>
@@ -5397,13 +5670,13 @@
           <t>Special Income Charges</t>
         </is>
       </c>
-      <c r="B35" s="29" t="n">
+      <c r="B35" s="25" t="n">
         <v>-740</v>
       </c>
-      <c r="C35" s="29" t="n">
+      <c r="C35" s="25" t="n">
         <v>-24</v>
       </c>
-      <c r="D35" s="29" t="n">
+      <c r="D35" s="25" t="n">
         <v>-1884</v>
       </c>
     </row>
@@ -5413,13 +5686,13 @@
           <t>Gain On Sale Of Business</t>
         </is>
       </c>
-      <c r="B36" s="29" t="n">
+      <c r="B36" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="C36" s="29" t="n">
+      <c r="C36" s="25" t="n">
         <v>-64</v>
       </c>
-      <c r="D36" s="29" t="n">
+      <c r="D36" s="25" t="n">
         <v>-33</v>
       </c>
     </row>
@@ -5429,13 +5702,13 @@
           <t>Impairment Of Capital Assets</t>
         </is>
       </c>
-      <c r="B37" s="29" t="n">
+      <c r="B37" s="25" t="n">
         <v>671</v>
       </c>
-      <c r="C37" s="29" t="n">
+      <c r="C37" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="D37" s="29" t="n">
+      <c r="D37" s="25" t="n">
         <v>1830</v>
       </c>
     </row>
@@ -5445,13 +5718,13 @@
           <t>Restructuring And Mergern Acquisition</t>
         </is>
       </c>
-      <c r="B38" s="29" t="n">
+      <c r="B38" s="25" t="n">
         <v>69</v>
       </c>
-      <c r="C38" s="29" t="n">
+      <c r="C38" s="25" t="n">
         <v>-40</v>
       </c>
-      <c r="D38" s="29" t="n">
+      <c r="D38" s="25" t="n">
         <v>21</v>
       </c>
     </row>
@@ -5461,13 +5734,13 @@
           <t>Net Non Operating Interest Income Expense</t>
         </is>
       </c>
-      <c r="B39" s="29" t="n">
+      <c r="B39" s="25" t="n">
         <v>-10</v>
       </c>
-      <c r="C39" s="29" t="n">
+      <c r="C39" s="25" t="n">
         <v>-28</v>
       </c>
-      <c r="D39" s="29" t="n">
+      <c r="D39" s="25" t="n">
         <v>-41</v>
       </c>
     </row>
@@ -5477,13 +5750,13 @@
           <t>Interest Expense Non Operating</t>
         </is>
       </c>
-      <c r="B40" s="29" t="n">
+      <c r="B40" s="25" t="n">
         <v>31</v>
       </c>
-      <c r="C40" s="29" t="n">
+      <c r="C40" s="25" t="n">
         <v>40</v>
       </c>
-      <c r="D40" s="29" t="n">
+      <c r="D40" s="25" t="n">
         <v>63</v>
       </c>
     </row>
@@ -5493,13 +5766,13 @@
           <t>Interest Income Non Operating</t>
         </is>
       </c>
-      <c r="B41" s="29" t="n">
+      <c r="B41" s="25" t="n">
         <v>21</v>
       </c>
-      <c r="C41" s="29" t="n">
+      <c r="C41" s="25" t="n">
         <v>12</v>
       </c>
-      <c r="D41" s="29" t="n">
+      <c r="D41" s="25" t="n">
         <v>22</v>
       </c>
     </row>
@@ -5509,13 +5782,13 @@
           <t>Operating Income</t>
         </is>
       </c>
-      <c r="B42" s="29" t="n">
+      <c r="B42" s="25" t="n">
         <v>-1295</v>
       </c>
-      <c r="C42" s="29" t="n">
+      <c r="C42" s="25" t="n">
         <v>-444</v>
       </c>
-      <c r="D42" s="29" t="n">
+      <c r="D42" s="25" t="n">
         <v>507</v>
       </c>
     </row>
@@ -5525,13 +5798,13 @@
           <t>Operating Expense</t>
         </is>
       </c>
-      <c r="B43" s="29" t="n">
+      <c r="B43" s="25" t="n">
         <v>1725</v>
       </c>
-      <c r="C43" s="29" t="n">
+      <c r="C43" s="25" t="n">
         <v>1516</v>
       </c>
-      <c r="D43" s="29" t="n">
+      <c r="D43" s="25" t="n">
         <v>1705</v>
       </c>
     </row>
@@ -5541,13 +5814,13 @@
           <t>Research And Development</t>
         </is>
       </c>
-      <c r="B44" s="29" t="n">
+      <c r="B44" s="25" t="n">
         <v>1167</v>
       </c>
-      <c r="C44" s="29" t="n">
+      <c r="C44" s="25" t="n">
         <v>1061</v>
       </c>
-      <c r="D44" s="29" t="n">
+      <c r="D44" s="25" t="n">
         <v>1132</v>
       </c>
     </row>
@@ -5557,13 +5830,13 @@
           <t>Selling General And Administration</t>
         </is>
       </c>
-      <c r="B45" s="29" t="n">
+      <c r="B45" s="25" t="n">
         <v>558</v>
       </c>
-      <c r="C45" s="29" t="n">
+      <c r="C45" s="25" t="n">
         <v>455</v>
       </c>
-      <c r="D45" s="29" t="n">
+      <c r="D45" s="25" t="n">
         <v>573</v>
       </c>
     </row>
@@ -5573,13 +5846,13 @@
           <t>Gross Profit</t>
         </is>
       </c>
-      <c r="B46" s="29" t="n">
+      <c r="B46" s="25" t="n">
         <v>430</v>
       </c>
-      <c r="C46" s="29" t="n">
+      <c r="C46" s="25" t="n">
         <v>1072</v>
       </c>
-      <c r="D46" s="29" t="n">
+      <c r="D46" s="25" t="n">
         <v>2212</v>
       </c>
     </row>
@@ -5589,13 +5862,13 @@
           <t>Cost Of Revenue</t>
         </is>
       </c>
-      <c r="B47" s="29" t="n">
+      <c r="B47" s="25" t="n">
         <v>5656</v>
       </c>
-      <c r="C47" s="29" t="n">
+      <c r="C47" s="25" t="n">
         <v>5591</v>
       </c>
-      <c r="D47" s="29" t="n">
+      <c r="D47" s="25" t="n">
         <v>5143</v>
       </c>
     </row>
@@ -5605,13 +5878,13 @@
           <t>Total Revenue</t>
         </is>
       </c>
-      <c r="B48" s="29" t="n">
+      <c r="B48" s="25" t="n">
         <v>6086</v>
       </c>
-      <c r="C48" s="29" t="n">
+      <c r="C48" s="25" t="n">
         <v>6663</v>
       </c>
-      <c r="D48" s="29" t="n">
+      <c r="D48" s="25" t="n">
         <v>7355</v>
       </c>
     </row>
@@ -5621,13 +5894,13 @@
           <t>Operating Revenue</t>
         </is>
       </c>
-      <c r="B49" s="29" t="n">
+      <c r="B49" s="25" t="n">
         <v>6086</v>
       </c>
-      <c r="C49" s="29" t="n">
+      <c r="C49" s="25" t="n">
         <v>6663</v>
       </c>
-      <c r="D49" s="29" t="n">
+      <c r="D49" s="25" t="n">
         <v>7355</v>
       </c>
     </row>

--- a/docs/reports/SNDK.xlsx
+++ b/docs/reports/SNDK.xlsx
@@ -611,7 +611,7 @@
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>1343.662376005138</v>
+        <v>1221.647997303362</v>
       </c>
     </row>
     <row r="8">
@@ -2566,7 +2566,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -2641,20 +2641,20 @@
         </is>
       </c>
       <c r="C5" s="6" t="n">
-        <v>497.0336741547966</v>
+        <v>537.1708965093026</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>399.777015638166</v>
+        <v>430.7573165639816</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>609.0982264335238</v>
+        <v>659.7098172138393</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>0.2028985507246377</v>
+        <v>0.3888888888888889</v>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>ok — down-weighted: 0.4x the median of the other lenses</t>
+          <t>ok</t>
         </is>
       </c>
     </row>
@@ -2679,7 +2679,7 @@
         <v>1637.628897273374</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>0.4347826086956522</v>
+        <v>0.3333333333333334</v>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
@@ -2708,7 +2708,7 @@
         <v>1375.278619392698</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>0.3623188405797102</v>
+        <v>0.2777777777777778</v>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
@@ -2817,7 +2817,7 @@
         </is>
       </c>
       <c r="B18" s="6" t="n">
-        <v>1343.662376005138</v>
+        <v>1221.647997303362</v>
       </c>
     </row>
     <row r="20">
@@ -2830,14 +2830,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>Discounted cash flow (FCFF) sits 0.4x the lens median and was down-weighted by 60%.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>Target anchored 15% to the Street consensus ($1,975.95); model-only target $1,232.08.</t>
+          <t>Target anchored 15% to the Street consensus ($1,975.95); model-only target $1,088.54.</t>
         </is>
       </c>
     </row>
@@ -2952,28 +2945,28 @@
         <v>48130</v>
       </c>
       <c r="D5" s="19" t="n">
-        <v>52146.48516853159</v>
+        <v>53863.53768345222</v>
       </c>
       <c r="E5" s="19" t="n">
-        <v>55546.12408119863</v>
+        <v>59233.44643308645</v>
       </c>
       <c r="F5" s="19" t="n">
-        <v>58470.05309974719</v>
+        <v>64080.05595404876</v>
       </c>
       <c r="G5" s="19" t="n">
-        <v>61043.12004096285</v>
+        <v>68287.46527387545</v>
       </c>
       <c r="H5" s="19" t="n">
-        <v>63367.03086927003</v>
+        <v>71798.02561770397</v>
       </c>
       <c r="I5" s="19" t="n">
-        <v>65520.72769967289</v>
+        <v>74625.07287640104</v>
       </c>
       <c r="J5" s="19" t="n">
-        <v>67563.6912192493</v>
+        <v>76869.9689441802</v>
       </c>
       <c r="K5" s="19" t="n">
-        <v>69252.78349973053</v>
+        <v>78791.7181677847</v>
       </c>
     </row>
     <row r="6">
@@ -3121,28 +3114,28 @@
         <v>30279.91281826</v>
       </c>
       <c r="D9" s="19" t="n">
-        <v>11997.95268372662</v>
+        <v>12394.57089287301</v>
       </c>
       <c r="E9" s="19" t="n">
-        <v>11032.84812650948</v>
+        <v>11768.37907774677</v>
       </c>
       <c r="F9" s="19" t="n">
-        <v>9773.581597473492</v>
+        <v>10715.85700809185</v>
       </c>
       <c r="G9" s="19" t="n">
-        <v>8282.160712834846</v>
+        <v>9270.660755919216</v>
       </c>
       <c r="H9" s="19" t="n">
-        <v>6602.427694339863</v>
+        <v>7487.16849646802</v>
       </c>
       <c r="I9" s="19" t="n">
-        <v>4763.7333764776</v>
+        <v>5432.237143708681</v>
       </c>
       <c r="J9" s="19" t="n">
-        <v>4913.741837563135</v>
+        <v>5597.072884140474</v>
       </c>
       <c r="K9" s="19" t="n">
-        <v>5037.766633502212</v>
+        <v>5738.180956243985</v>
       </c>
     </row>
     <row r="10">
@@ -3205,28 +3198,28 @@
         <v>8918.077482256851</v>
       </c>
       <c r="D12" s="20" t="n">
-        <v>11900.35014518295</v>
+        <v>12057.54522436101</v>
       </c>
       <c r="E12" s="20" t="n">
-        <v>10949.38082594039</v>
+        <v>11419.34521236998</v>
       </c>
       <c r="F12" s="20" t="n">
-        <v>9667.012762287175</v>
+        <v>10354.30763523472</v>
       </c>
       <c r="G12" s="20" t="n">
-        <v>8120.974262642939</v>
+        <v>8892.264943251726</v>
       </c>
       <c r="H12" s="20" t="n">
-        <v>6360.818269060845</v>
+        <v>7082.631372696337</v>
       </c>
       <c r="I12" s="20" t="n">
-        <v>4420.748553466789</v>
+        <v>4985.836949915931</v>
       </c>
       <c r="J12" s="20" t="n">
-        <v>4452.207158416158</v>
+        <v>5083.810330971072</v>
       </c>
       <c r="K12" s="20" t="n">
-        <v>4487.321313369473</v>
+        <v>5111.91685047207</v>
       </c>
     </row>
     <row r="13">
@@ -3563,25 +3556,25 @@
         <v>1.434496712190187</v>
       </c>
       <c r="D26" s="11" t="n">
-        <v>0.08345076186435872</v>
+        <v>0.119126068636032</v>
       </c>
       <c r="E26" s="11" t="n">
-        <v>0.06519401838263497</v>
+        <v>0.09969469107640785</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>0.05263965878653004</v>
+        <v>0.08182217670615058</v>
       </c>
       <c r="G26" s="11" t="n">
-        <v>0.04400657780874821</v>
+        <v>0.06565863991822649</v>
       </c>
       <c r="H26" s="11" t="n">
-        <v>0.03806998768653584</v>
+        <v>0.05140856128938115</v>
       </c>
       <c r="I26" s="11" t="n">
-        <v>0.0339876557392448</v>
+        <v>0.03937500000000001</v>
       </c>
       <c r="J26" s="11" t="n">
-        <v>0.03118041559215805</v>
+        <v>0.03008232998977831</v>
       </c>
       <c r="K26" s="11" t="n">
         <v>0.025</v>
